--- a/Preckon_Module_Completion.xlsx
+++ b/Preckon_Module_Completion.xlsx
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'TenderLogix'!$A$4:$G$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DocLogix'!$A$4:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DocLogix'!$A$4:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DrawLogix'!$A$4:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QuantLogix'!$A$4:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CostLogix'!$A$4:$G$12</definedName>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ProcureLogix'!$A$4:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'NarrativeLogix'!$A$4:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Platform-Core'!$A$4:$G$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'P0 Backlog'!$A$4:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'P0 Backlog'!$A$4:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -88,7 +88,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -107,12 +107,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,11 +123,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E1F5FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1C4E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,19 +195,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -832,28 +824,28 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.232</v>
+        <v>0.8</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>█████░░░░░░░░░░░░░░░</t>
+          <t>████████████████░░░░</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Clause extraction is genuinely good. Everything that makes it a CDE - register, numbering, revisions, transmittals - does not exist. The Knowledge Graph roadmap depends on this module first.</t>
+          <t>Built out on 20 Aug from 23%. Register, numbering, revisions, transmittals, revision diff, retrieval, review, distribution and retention all work and are deployed. The honest limit: most of it is reachable only through the API, and OCR is absent.</t>
         </is>
       </c>
     </row>
@@ -927,7 +919,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Measurement, BOQ and reconciliation are solid. Traceability stops at PCM objects because source_region does not exist.</t>
+          <t>Measurement, BOQ and reconciliation are solid. source_region now exists, so the headline click-a-quantity-see-the-drawing claim is unblocked at the data layer - takeoff still has to write the regions.</t>
         </is>
       </c>
     </row>
@@ -954,7 +946,7 @@
       <c r="F9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="10" t="n">
         <v>0.188</v>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -991,7 +983,7 @@
       <c r="F10" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="10" t="n">
         <v>0.267</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -1028,7 +1020,7 @@
       <c r="F11" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="10" t="n">
         <v>0.167</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -1065,7 +1057,7 @@
       <c r="F12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="9" t="n">
         <v>0.833</v>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1097,13 +1089,13 @@
         <v>15</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.429</v>
+        <v>0.436</v>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
@@ -1128,23 +1120,23 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.412</v>
+        <v>0.477</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>████████░░░░░░░░░░░░</t>
+          <t>██████████░░░░░░░░░░</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -1184,14 +1176,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Platform / Core - 43% complete</t>
+          <t>Platform / Core - 44% complete</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Identity, tenancy, audit, AI governance, operations.  39 features audited: 15 done, 3 partial, 21 missing.</t>
+          <t>Identity, tenancy, audit, AI governance, operations.  39 features audited: 15 done, 4 partial, 20 missing.</t>
         </is>
       </c>
     </row>
@@ -1872,19 +1864,19 @@
           <t>Retrieval / RAG</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>Scaffolded</t>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>chunk table with embedding column and FULLTEXT index.</t>
+          <t>retrieval.ts + index-store.ts write and search the chunk table; revision-aware, budget-packed. 34 tests.</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Nothing reads or writes it. Retrieval is schema-only.</t>
+          <t>Wired for DocLogix only. No embeddings generated, and the AI worker does not call it yet - so agents still answer from the envelope.</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -1894,7 +1886,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2820,22 +2812,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>File storage and versioning</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>Screens for register, review, transmittals and search</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Missing</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Plain file store. No controlled-vs-uncontrolled distinction, no folder or metadata views.</t>
+          <t>Everything built today is reachable only through the API. This is the honest limit on calling the module done.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
@@ -2847,27 +2839,27 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>DocLogix</t>
+          <t>QuantLogix</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Intelligent document register (35+ controlled fields)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>BOQ line to source object trace</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>The core object of the module. No document number, discipline, originator, suitability, status or distribution.</t>
+          <t>The anchor exists but QuantLogix does not write regions yet - takeoff must record the polygon it measured.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -2879,12 +2871,12 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>DocLogix</t>
+          <t>QuantLogix</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Document numbering engine</t>
+          <t>Click a quantity, highlight contributing objects</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -2894,7 +2886,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>No configurable schemes, segment validation, auto-increment, reserved ranges or duplicate detection.</t>
+          <t>No longer blocked at the data layer. Needs takeoff to write regions and the editor to highlight them.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2911,12 +2903,12 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>DocLogix</t>
+          <t>Platform / Core</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Formal revision vs file version</t>
+          <t>SSO (SAML / OIDC)</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -2926,12 +2918,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>No current/superseded semantics, no purpose-of-issue, no immutable superseded revisions.</t>
+          <t>Enterprise deal blocker. Named in Complete Platform section 15.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
@@ -2943,12 +2935,12 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>DocLogix</t>
+          <t>Platform / Core</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Transmittal management</t>
+          <t>MFA</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -2958,7 +2950,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Transmittals are a formal contractual record with acknowledgements. Entirely absent.</t>
+          <t>Enterprise deal blocker.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -2975,27 +2967,27 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>DocLogix</t>
+          <t>Platform / Core</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Semantic / natural-language project search</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>Scaffolded</t>
+          <t>Per-attempt usage ledger</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Missing</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>NOTHING reads or writes chunk. No ingestion, chunking, embedding or retrieval code exists.</t>
+          <t>A retry overwrites the previous attempt tokens, so failed-attempt spend is invisible and AI cost is under-counted today.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
@@ -3007,12 +2999,12 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>DocLogix</t>
+          <t>Platform / Core</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Document-region provenance anchor</t>
+          <t>Tenant AI policy and data sensitivity</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -3022,12 +3014,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>source_region (page + polygon) is the linchpin for click-a-quantity-see-the-clause. Claimed in 4 documents.</t>
+          <t>Blocks Preckon Private AI and Sovereign AI as sellable products.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -3039,12 +3031,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>QuantLogix</t>
+          <t>Platform / Core</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>BOQ line to source object trace</t>
+          <t>Retrieval / RAG</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
@@ -3054,7 +3046,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Trace reaches PCM objects but not the drawing region that produced them (no source_region).</t>
+          <t>Wired for DocLogix only. No embeddings generated, and the AI worker does not call it yet - so agents still answer from the envelope.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -3071,27 +3063,27 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>QuantLogix</t>
+          <t>Platform / Core</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Click a quantity, highlight contributing objects</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>AI cost reporting</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>The headline traceability claim in four documents. Blocked on source_region.</t>
+          <t>Built on under-counted data until the per-attempt ledger exists.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -3108,7 +3100,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>SSO (SAML / OIDC)</t>
+          <t>CI running the test suite</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
@@ -3118,12 +3110,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Enterprise deal blocker. Named in Complete Platform section 15.</t>
+          <t>426 tests and six quality gates run only on a developer machine.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -3140,7 +3132,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>MFA</t>
+          <t>Automated backup and tested restore</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -3150,12 +3142,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Enterprise deal blocker.</t>
+          <t>An untested restore is not a backup.</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
@@ -3172,7 +3164,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Per-attempt usage ledger</t>
+          <t>Staging environment</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -3182,12 +3174,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>A retry overwrites the previous attempt tokens, so failed-attempt spend is invisible and AI cost is under-counted today.</t>
+          <t>Changes are currently validated in production.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
@@ -3204,7 +3196,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Tenant AI policy and data sensitivity</t>
+          <t>Branch protection and PR review</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -3214,12 +3206,12 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Blocks Preckon Private AI and Sovereign AI as sellable products.</t>
+          <t>No review gate on production code.</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
@@ -3236,17 +3228,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Retrieval / RAG</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>Scaffolded</t>
+          <t>Encryption at rest and key management</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Missing</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Nothing reads or writes it. Retrieval is schema-only.</t>
+          <t>Named in Complete Platform section 15.</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -3268,17 +3260,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>AI cost reporting</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>Credential rotation</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Missing</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Built on under-counted data until the per-attempt ledger exists.</t>
+          <t>Rotate everything ever committed; confirm the production DB password is not the default.</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -3300,17 +3292,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>CI running the test suite</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>Port hardening</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>426 tests and six quality gates run only on a developer machine.</t>
+          <t>3307 (MySQL), 11434 (Ollama, unauthenticated) and 5000 bind 0.0.0.0; only the provider firewall stops them.</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -3324,200 +3316,8 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Platform / Core</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Automated backup and tested restore</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>An untested restore is not a backup.</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Platform / Core</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Staging environment</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Changes are currently validated in production.</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Platform / Core</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Branch protection and PR review</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>No review gate on production code.</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Platform / Core</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Encryption at rest and key management</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Named in Complete Platform section 15.</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>Platform / Core</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Credential rotation</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Rotate everything ever committed; confirm the production DB password is not the default.</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Platform / Core</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Port hardening</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>3307 (MySQL), 11434 (Ollama, unauthenticated) and 5000 bind 0.0.0.0; only the provider firewall stops them.</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F28"/>
+  <autoFilter ref="A4:F22"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -3532,7 +3332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3577,7 +3377,7 @@
           <t>Modules seeded</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3594,7 +3394,7 @@
           <t>Artifact types</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -3611,7 +3411,7 @@
           <t>AI agents</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -3628,14 +3428,14 @@
           <t>Workflows</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>One per module plus 6 TenderLogix sub-workflows (classify, riskreview, clarificationloop, bidqualification, bidassembly, skeleton)</t>
+          <t>One per module plus 6 TenderLogix sub-workflows</t>
         </is>
       </c>
     </row>
@@ -3645,148 +3445,165 @@
           <t>Database tables</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>56</t>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>71</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Includes 12 pcm_* tables, artifact + provenance, audit_event + audit_chain, event_outbox, ai_job</t>
+          <t>Was 56 on 19 Aug. DocLogix added 12: register, revisions, transmittal x3, source_region, numbering_scheme, distribution x2, review x2, comments</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>API routes</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>78</t>
+          <t>Migrations</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Next.js App Router handlers under src/app/api</t>
+          <t>019 and 020 are DocLogix; both validated against MySQL 8 in a scratch database, 020 re-run to prove idempotency</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Module surfaces</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>API routes</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>87</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>boq, drawings, estimate, narrative, procurement, schedule, specs, tender, common, generic</t>
+          <t>Was 78. Seven new DocLogix endpoints plus search</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Tests</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>426 passing</t>
+          <t>Module surfaces</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>23 files plus Playwright golden-path E2E. One pre-existing failure needs Docker MySQL on 3308.</t>
+          <t>boq, drawings, estimate, narrative, procurement, schedule, specs, tender, common, generic - none yet for the DocLogix register</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Deterministic engines</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>632 passing</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>cpm.ts, pcm/measure.ts, boq/reconcile.ts, cad/compare.ts, cad/impact.ts, standards.ts, validate.ts</t>
+          <t>29 files. Was 426 on 19 Aug; DocLogix added 206. One pre-existing failure needs Docker MySQL on 3308.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Live sheets in production</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>31</t>
+          <t>Deterministic engines</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Average 8.1 MB, largest 37 MB - a real performance concern for the drawing editor</t>
+          <t>cpm, pcm/measure, boq/reconcile, cad/compare, cad/impact, standards, validate, doc/numbering, doc/revision, doc/compare, doc/retrieval</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Deployed versions</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>next 15.5.23</t>
+          <t>Live sheets in production</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>postcss 8.5.26 - both verified inside the running container</t>
+          <t>Average 8.1 MB, largest 37 MB - still the biggest user-facing performance issue</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>CI runs</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>Deployed versions</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>next 15.5.23</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Six workflow files exist; none has ever executed</t>
+          <t>postcss 8.5.26 - verified inside the running container</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
+          <t>CI runs</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Six workflow files exist; none has ever executed. 632 tests run only on a developer machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
           <t>ADRs</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>50 are specified across three blueprints</t>
         </is>
@@ -4552,7 +4369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4567,14 +4384,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DocLogix - 23% complete</t>
+          <t>DocLogix - 80% complete</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CDE, document control and document intelligence.  14 features audited: 1 done, 4 partial, 9 missing.</t>
+          <t>CDE, document control and document intelligence.  15 features audited: 11 done, 2 partial, 2 missing.</t>
         </is>
       </c>
     </row>
@@ -4623,22 +4440,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>File storage and versioning</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>File storage and binary versioning</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>file, file_page tables; upload and retrieval endpoints.</t>
+          <t>file + file_page; document_revision.file_version bumps when the file is replaced without the revision changing.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Plain file store. No controlled-vs-uncontrolled distinction, no folder or metadata views.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
@@ -4648,7 +4465,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4663,19 +4480,19 @@
           <t>Intelligent document register (35+ controlled fields)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>document artifact type exists but is an AI output, not a controlled register record.</t>
+          <t>document_register - number, title, type, discipline, originator, volume, level, zone, package, confidentiality, status, retention, required_by. Registers before a file exists.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>The core object of the module. No document number, discipline, originator, suitability, status or distribution.</t>
+          <t>API only - no register screen yet.</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
@@ -4685,7 +4502,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -4700,19 +4517,19 @@
           <t>Document numbering engine</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>numbering.ts - schemes as data, segment validation, reserved ranges, sequence allocation, legacy adoption. Duplicates blocked by a unique index, not an app check that races. 33 tests.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>No configurable schemes, segment validation, auto-increment, reserved ranges or duplicate detection.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
@@ -4722,7 +4539,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4737,19 +4554,19 @@
           <t>Formal revision vs file version</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>revision.ts - alpha/numeric/ISO 19650, I and O skipped, C outranks P, supersession planned then applied atomically. 32 tests.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>No current/superseded semantics, no purpose-of-issue, no immutable superseded revisions.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -4759,7 +4576,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4774,19 +4591,19 @@
           <t>Revision intelligence (change classification)</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>cad/compare.ts diffs DXF revisions; cad/impact.ts gives affected/unaffected/unknown verdicts. 39 tests.</t>
+          <t>compare.ts - deterministic LCS diff over extracted text, classified as dimension/requirement/commercial/reference/note, significant-first review order. 28 tests.</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Works for CAD only. No document or text revision comparison, no change classification taxonomy.</t>
+          <t>Text only. Drawing-geometry diff is cad/compare.ts; the two are not yet joined into one report.</t>
         </is>
       </c>
       <c r="F9" s="18" t="inlineStr">
@@ -4796,7 +4613,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4635,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>workflow, workflow_run, workflow_run_step tables; workflow.doclogix seeded.</t>
+          <t>document_review with stage, min_approvals, due_at; contractual response codes; issue gate. 44 tests with review.ts.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Generic engine only. No document states (WIP-Shared-Approved-IFC-Superseded), no SLA, escalation or approval matrices.</t>
+          <t>No escalation, no reminders, no conditional branching. The SLA date exists and nothing acts on it.</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
@@ -4833,7 +4650,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4672,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>review-queue endpoints; deviations approve/reject.</t>
+          <t>document_review + document_review_assignee + document_comment; comments pinned to a source_region, threaded, blocking flag; decision log.</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>No three-panel document review UI, no markup, no comments pinned to a region, no decision log.</t>
+          <t>Backend complete, no UI. A reviewer cannot reach any of it without an API client.</t>
         </is>
       </c>
       <c r="F11" s="18" t="inlineStr">
@@ -4885,19 +4702,19 @@
           <t>Transmittal management</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>transmittal + item + recipient; carries revisions not documents; sending freezes; acknowledgements; recall never deletes. 35 tests.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Transmittals are a formal contractual record with acknowledgements. Entirely absent.</t>
+          <t>API only - no transmittal screen.</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
@@ -4907,7 +4724,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4751,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Genuinely working and the module's strongest feature.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -4966,12 +4783,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>CAD extraction service handles drawings only.</t>
+          <t>CAD extraction handles drawings only.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>No OCR for scanned PDFs, Office formats, email or images.</t>
+          <t>No OCR for scanned PDFs, Office formats, email or images. Anything not already text-extracted is invisible to search.</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
@@ -4996,19 +4813,19 @@
           <t>Semantic / natural-language project search</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>Scaffolded</t>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>chunk table exists with embedding column and FULLTEXT index.</t>
+          <t>retrieval.ts + index-store.ts - meaning-based chunking, hybrid ranking, budget packing, revision-aware. The chunk table finally has a writer. 34 tests.</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>NOTHING reads or writes chunk. No ingestion, chunking, embedding or retrieval code exists.</t>
+          <t>No embeddings generated yet, so ranking is lexical plus identifier matching. The column and the cosine function are ready for them.</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -5018,7 +4835,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -5033,19 +4850,19 @@
           <t>Document-region provenance anchor</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>artifact_provenance and trace endpoints exist but anchor to artifacts, not document regions.</t>
+          <t>source_region - page, polygon, text range or model object, cited by entity_type/entity_id, with method and confidence.</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>source_region (page + polygon) is the linchpin for click-a-quantity-see-the-clause. Claimed in 4 documents.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -5055,7 +4872,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5070,14 +4887,14 @@
           <t>Distribution lists and controlled issue</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>distribution_list + distribution_member with to/cc, applies_to filters for when a list is offered.</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -5092,7 +4909,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5107,34 +4924,71 @@
           <t>Retention categories and legal hold</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>retention.ts - hold outranks retention including expired retention; live references block; no policy is not permission. Nothing deletes, it answers whether deletion is permitted.</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Screens for register, review, transmittals and search</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>None.</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Enterprise records requirement.</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>M</t>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>surfaces/drawings.tsx still renders the old file list.</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Everything built today is reachable only through the API. This is the honest limit on calling the module done.</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G18"/>
+  <autoFilter ref="A4:G19"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -6123,12 +5977,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>pcm_boq_map, pcm_quantity, artifact_provenance, /artifacts/[id]/trace and /pcm/objects/[oid]/trace.</t>
+          <t>pcm_boq_map, pcm_quantity, artifact_provenance, trace endpoints; source_region now exists and is deployed.</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Trace reaches PCM objects but not the drawing region that produced them (no source_region).</t>
+          <t>The anchor exists but QuantLogix does not write regions yet - takeoff must record the polygon it measured.</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
@@ -6160,12 +6014,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>source_region table deployed 20 Aug; regionsFor() reads the evidence behind any entity.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>The headline traceability claim in four documents. Blocked on source_region.</t>
+          <t>No longer blocked at the data layer. Needs takeoff to write regions and the editor to highlight them.</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">

--- a/Preckon_Module_Completion.xlsx
+++ b/Preckon_Module_Completion.xlsx
@@ -29,8 +29,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'ScheduleLogix'!$A$4:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ProcureLogix'!$A$4:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'NarrativeLogix'!$A$4:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Platform-Core'!$A$4:$G$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'P0 Backlog'!$A$4:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Platform-Core'!$A$4:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'P0 Backlog'!$A$4:$F$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -288,7 +288,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -724,10 +723,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every feature verified against the codebase and the deployed database on 20 Aug 2026. Weighted: Done 1.0, Partial 0.5, Scaffolded 0.25, Missing 0.</t>
-        </is>
-      </c>
-    </row>
+          <t>Every feature verified against the codebase and the deployed database on 20 Aug 2026, after the 13:00 deploy (app and worker rebuilt, all 21 migrations applied, DocLogix and AI-governance tables live). Weighted: Done 1.0, Partial 0.5, Scaffolded 0.25, Missing 0. This revision recounts every module from its own rows and regrades three AI-governance features from Done to Partial - policy, budgets and the usage ledger have code and tables but no caller, which is the same basis on which the cache was already Partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1083,31 +1083,32 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.436</v>
+        <v>0.55</v>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>█████████░░░░░░░░░░░</t>
+          <t>███████████░░░░░░░░░</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Trust foundations are strong: audit chain, tenant isolation, durable jobs, provenance. AI governance and enterprise ops are the gaps.</t>
-        </is>
-      </c>
-    </row>
+          <t>Trust foundations are strong: audit chain, tenant isolation, durable jobs, provenance. The AI governance layer landed on 20 Aug - policy, model registry, prompt versions, budgets, cache and usage ledger all have code and live tables - but nothing imports any of it yet, so it is graded Partial: built, not yet enforced. Enterprise ops remain the real gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
@@ -1120,19 +1121,19 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.477</v>
+        <v>0.511</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
@@ -1161,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1176,17 +1177,18 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Platform / Core - 44% complete</t>
+          <t>Platform / Core - 55% complete</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Identity, tenancy, audit, AI governance, operations.  39 features audited: 15 done, 4 partial, 20 missing.</t>
-        </is>
-      </c>
-    </row>
+          <t>Identity, tenancy, audit, AI governance, operations.  40 features audited: 19 done, 9 partial, 12 missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1642,19 +1644,19 @@
           <t>Per-attempt usage ledger</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>ai_job holds one MUTABLE row per job.</t>
+          <t>ai_usage_ledger - append-only, one row per attempt, with model alias, prompt version, sensitivity, policy version, cost and outcome. Migration 021.</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>A retry overwrites the previous attempt tokens, so failed-attempt spend is invisible and AI cost is under-counted today.</t>
+          <t>No writer: ai_usage_ledger has no INSERT site in src/. Table is live; nothing records to it.</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -1679,19 +1681,19 @@
           <t>Tenant AI policy and data sensitivity</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>No sensitivity field anywhere in src.</t>
+          <t>ai/policy.ts + ai_tenant_policy - deployment modes, per-classification boundaries, eligibility before scoring, tenant may narrow never widen. 47 tests.</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Blocks Preckon Private AI and Sovereign AI as sellable products.</t>
+          <t>Not imported by any file. Policy that nothing consults does not constrain anything.</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
@@ -1716,19 +1718,19 @@
           <t>Model registry and aliases</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Model names hard-coded in 3 routes and jobs.ts.</t>
+          <t>ai/registry.ts + ai_model_registry - aliases, capabilities, rate cards, loud failure on unknown alias. 37 tests with cache.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Application code must reference aliases, not claude-opus-4-8.</t>
+          <t>The four files naming concrete models are not yet migrated to aliases.</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
@@ -1753,19 +1755,19 @@
           <t>Prompt registry with versions</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Prompts are strings in worker/src/prompts.mjs.</t>
+          <t>ai_prompt_version table with prompt_key, version, task_type, prefix hash and approval status.</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>AI Fabric section 18 forbids untracked prompt strings in source.</t>
+          <t>The worker still reads its prompts from source; nothing populates the table yet.</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
@@ -1790,19 +1792,19 @@
           <t>Budgets (token, cost, latency)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>ai/budget.ts - estimate before running, tenant limits, clamping, remedies in the order section 21 recommends. 47 tests with policy.</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Router must reject or re-route when a budget would be exceeded.</t>
+          <t>Not imported by any file. A budget nothing checks caps nothing.</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
@@ -1827,19 +1829,19 @@
           <t>Response cache (exact, semantic, artifact)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>ai/cache.ts + ai_response_cache - every answer-changing dimension in the key, scoped invalidation triggers. 37 tests.</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>No cache layer of any kind.</t>
+          <t>Keys and safety rules exist; nothing reads or writes the table yet.</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
@@ -2209,7 +2211,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>426 tests and six quality gates run only on a developer machine.</t>
+          <t>426 tests and six quality gates run only on a developer machine. The publishing token also lacks `workflow` scope, so ci.yml cannot even be pushed to techsmeinc/preckon-tenant - the mirror carries no .github at all.</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr">
@@ -2342,7 +2344,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Repeatable deploy</t>
+          <t>schema.sql / migration drift guard</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
@@ -2352,7 +2354,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>deploy.ps1 - sha256-verified resumable upload, migrations, catalog seed gate, worker rebuild.</t>
+          <t>schema-drift.test.ts - fails if a migration creates a table schema.sql does not declare. Found 5 tables drifted since migration 004 whose queries had never been tenant-checked.</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2374,27 +2376,27 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Encryption at rest and key management</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>Repeatable deploy</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>deploy.ps1 - sha256-verified resumable upload, migrations, catalog seed gate, worker rebuild.</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Named in Complete Platform section 15.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
@@ -2404,7 +2406,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2418,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Secrets management (Vault / KMS)</t>
+          <t>Encryption at rest and key management</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
@@ -2426,22 +2428,22 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Secrets in .env on the host.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Named in Complete Platform section 15.</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2455,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Credential rotation</t>
+          <t>Secrets management (Vault / KMS)</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
@@ -2463,22 +2465,22 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Outstanding from the earlier security review.</t>
+          <t>Secrets in .env on the host.</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Rotate everything ever committed; confirm the production DB password is not the default.</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2492,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Upload malware scanning</t>
+          <t>Credential rotation</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
@@ -2500,22 +2502,22 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Outstanding from the earlier security review.</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Rotate everything ever committed; confirm the production DB password is not the default.</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2529,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Port hardening</t>
+          <t>Upload validation and scan gating</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
@@ -2537,138 +2539,175 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>3308, 4000 and 8081 bind to 127.0.0.1 and are externally closed.</t>
+          <t>upload-safety.ts - magic-number vs extension, blocked extensions, macro formats, path traversal, zip-bomb ratio, explicit scan states. 33 tests.</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>3307 (MySQL), 11434 (Ollama, unauthenticated) and 5000 bind 0.0.0.0; only the provider firewall stops them.</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>Explicitly not an antivirus. A real scanner still needs to sit behind it, and the upload route does not call this yet.</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Architecture Decision Records</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>Port hardening</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>No docs/adr directory.</t>
+          <t>3308, 4000 and 8081 bind to 127.0.0.1 and are externally closed.</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>50 ADRs are specified across three blueprints. Zero exist.</t>
-        </is>
-      </c>
-      <c r="F41" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>3307 (MySQL), 11434 (Ollama, unauthenticated) and 5000 bind 0.0.0.0; only the provider firewall stops them.</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Enterprise Integration Hub and connector SDK</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>Architecture Decision Records</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>integrations.ts is stub-level.</t>
+          <t>docs/adr - 8 ADRs covering the stack conflict, queue, AI authority, aliases, policy, ledger, cache safety and isolation.</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>No connector runtime, canonical mapping or reconciliation engine.</t>
-        </is>
-      </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>8 of the ~50 specified. The rest are unwritten, but the ones that settle live contradictions are done.</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise Integration Hub and connector SDK</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>integrations.ts is stub-level.</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>No connector runtime, canonical mapping or reconciliation engine.</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Cross-module knowledge graph</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>pcm_relationship with typed edges, source and confidence.</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>PCM-scoped only. No Doc-Draw-Quant-Cost-Schedule traversal, no lineage or downstream-impact APIs.</t>
         </is>
       </c>
-      <c r="F43" s="18" t="inlineStr">
+      <c r="F44" s="18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G43"/>
+  <autoFilter ref="A4:G44"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -2683,7 +2722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2972,22 +3011,22 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Per-attempt usage ledger</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>Retrieval / RAG</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>A retry overwrites the previous attempt tokens, so failed-attempt spend is invisible and AI cost is under-counted today.</t>
+          <t>Wired for DocLogix only. No embeddings generated, and the AI worker does not call it yet - so agents still answer from the envelope.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
@@ -3004,22 +3043,22 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Tenant AI policy and data sensitivity</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>AI cost reporting</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Blocks Preckon Private AI and Sovereign AI as sellable products.</t>
+          <t>Built on under-counted data until the per-attempt ledger exists.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -3036,22 +3075,22 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Retrieval / RAG</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>CI running the test suite</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Missing</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Wired for DocLogix only. No embeddings generated, and the AI worker does not call it yet - so agents still answer from the envelope.</t>
+          <t>426 tests and six quality gates run only on a developer machine.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
@@ -3068,22 +3107,22 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>AI cost reporting</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>Automated backup and tested restore</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Missing</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Built on under-counted data until the per-attempt ledger exists.</t>
+          <t>An untested restore is not a backup.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -3100,7 +3139,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>CI running the test suite</t>
+          <t>Staging environment</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
@@ -3110,12 +3149,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>426 tests and six quality gates run only on a developer machine.</t>
+          <t>Changes are currently validated in production.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -3132,7 +3171,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Automated backup and tested restore</t>
+          <t>Branch protection and PR review</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -3142,12 +3181,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>An untested restore is not a backup.</t>
+          <t>No review gate on production code.</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
@@ -3164,7 +3203,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Staging environment</t>
+          <t>Encryption at rest and key management</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -3174,12 +3213,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Changes are currently validated in production.</t>
+          <t>Named in Complete Platform section 15.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
@@ -3196,7 +3235,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Branch protection and PR review</t>
+          <t>Credential rotation</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -3206,7 +3245,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>No review gate on production code.</t>
+          <t>Rotate everything ever committed; confirm the production DB password is not the default.</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -3228,22 +3267,22 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Encryption at rest and key management</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
+          <t>Port hardening</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Named in Complete Platform section 15.</t>
+          <t>3307 (MySQL), 11434 (Ollama, unauthenticated) and 5000 bind 0.0.0.0; only the provider firewall stops them.</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
@@ -3252,72 +3291,8 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Platform / Core</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Credential rotation</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Rotate everything ever committed; confirm the production DB password is not the default.</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Platform / Core</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Port hardening</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>3307 (MySQL), 11434 (Ollama, unauthenticated) and 5000 bind 0.0.0.0; only the provider firewall stops them.</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F22"/>
+  <autoFilter ref="A4:F20"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -3447,7 +3422,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3464,7 +3439,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3515,12 +3490,12 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>632 passing</t>
+          <t>753 passing</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>29 files. Was 426 on 19 Aug; DocLogix added 206. One pre-existing failure needs Docker MySQL on 3308.</t>
+          <t>33 files. Was 426 on 19 Aug. DocLogix added 206, AI governance and upload safety a further 121. One pre-existing failure needs Docker MySQL on 3308.</t>
         </is>
       </c>
     </row>
@@ -3532,12 +3507,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>cpm, pcm/measure, boq/reconcile, cad/compare, cad/impact, standards, validate, doc/numbering, doc/revision, doc/compare, doc/retrieval</t>
+          <t>cpm, pcm/measure, boq/reconcile, cad/compare, cad/impact, standards, validate, doc/numbering, doc/revision, doc/compare, doc/retrieval, ai/policy, ai/budget, ai/cache, upload-safety</t>
         </is>
       </c>
     </row>
@@ -3600,12 +3575,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>50 are specified across three blueprints</t>
+          <t>Of ~50 specified. Cover the three-way stack conflict, queue choice, AI authority, model aliases, tenant policy, usage ledger, cache safety and tenant isolation.</t>
         </is>
       </c>
     </row>
@@ -3650,6 +3625,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4395,6 +4371,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5029,6 +5006,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5700,6 +5678,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6186,6 +6165,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6561,6 +6541,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7195,6 +7176,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7496,6 +7478,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>

--- a/Preckon_Module_Completion.xlsx
+++ b/Preckon_Module_Completion.xlsx
@@ -8,29 +8,30 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TenderLogix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DocLogix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DrawLogix" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuantLogix" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CostLogix" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScheduleLogix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProcureLogix" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NarrativeLogix" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform-Core" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P0 Backlog" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v1 Scope (P0)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TenderLogix" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DocLogix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DrawLogix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuantLogix" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CostLogix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScheduleLogix" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProcureLogix" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NarrativeLogix" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform-Core" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P0 Backlog" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'TenderLogix'!$A$4:$G$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DocLogix'!$A$4:$G$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DrawLogix'!$A$4:$G$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QuantLogix'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CostLogix'!$A$4:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'ScheduleLogix'!$A$4:$G$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ProcureLogix'!$A$4:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'NarrativeLogix'!$A$4:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Platform-Core'!$A$4:$G$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'P0 Backlog'!$A$4:$F$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TenderLogix'!$A$4:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DocLogix'!$A$4:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DrawLogix'!$A$4:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'QuantLogix'!$A$4:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CostLogix'!$A$4:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ScheduleLogix'!$A$4:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'ProcureLogix'!$A$4:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NarrativeLogix'!$A$4:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Platform-Core'!$A$4:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'P0 Backlog'!$A$4:$F$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,8 +88,20 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B1B2B"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -125,8 +138,23 @@
         <fgColor rgb="00E1F5FE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000B1B2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8FAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3E2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -148,11 +176,25 @@
         <color rgb="00CFD8DC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E3E8EF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E3E8EF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E3E8EF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E3E8EF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -209,6 +251,40 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -723,11 +799,10 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every feature verified against the codebase and the deployed database on 20 Aug 2026, after the 13:00 deploy (app and worker rebuilt, all 21 migrations applied, DocLogix and AI-governance tables live). Weighted: Done 1.0, Partial 0.5, Scaffolded 0.25, Missing 0. This revision recounts every module from its own rows and regrades three AI-governance features from Done to Partial - policy, budgets and the usage ledger have code and tables but no caller, which is the same basis on which the cache was already Partial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Every feature verified against the codebase and the deployed database on 20 Aug 2026, after the 14:45 deploy (app and worker rebuilt, 22 migrations applied, model registry seeded). Weighted: Done 1.0, Partial 0.5, Scaffolded 0.25, Missing 0. This revision moves four Platform features to Done because the AI governance layer is now called on the dispatch path rather than merely existing: ai/govern.ts is imported by jobs.ts, decisions are written to ai_usage_ledger, and 11 tests cover the decision matrix. Response cache and prompt registry stay Partial - still no caller.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1086,29 +1161,28 @@
         <v>40</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>███████████░░░░░░░░░</t>
+          <t>████████████░░░░░░░░</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Trust foundations are strong: audit chain, tenant isolation, durable jobs, provenance. The AI governance layer landed on 20 Aug - policy, model registry, prompt versions, budgets, cache and usage ledger all have code and live tables - but nothing imports any of it yet, so it is graded Partial: built, not yet enforced. Enterprise ops remain the real gap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>Trust foundations are strong: audit chain, tenant isolation, durable jobs, provenance. The AI governance layer is now WIRED, not just written: policy, model registry, budgets and the per-attempt usage ledger are consulted and recorded on every enqueue, deployed and seeded on 20 Aug. Enforcement stays behind a flag because unclassified data defaults to confidential, which saas mode forbids sending externally. Response cache and prompt registry remain unwired; enterprise ops (SSO, MFA, backups, staging, CI) are the real gap.</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
@@ -1124,20 +1198,20 @@
         <v>132</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>49</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.511</v>
+        <v>0.527</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>██████████░░░░░░░░░░</t>
+          <t>███████████░░░░░░░░░</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -1157,6 +1231,197 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NarrativeLogix - 83% complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Technical narrative and proposal writing.  3 features audited: 2 done, 1 partial, 0 missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Evidence in code / DB</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Gap - what is still needed</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Drafting</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Technical narrative sections</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>narrative_section artifact type; agent.narrative; workflow.narrativelogix; surfaces/narrative.tsx.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Export</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Narrative export to markdown</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>narrative/export.md endpoint.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Narrative grounded in project evidence</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Sections reference artifacts.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>No retrieval layer, so grounding is limited to what is passed in the envelope.</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1177,7 +1442,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Platform / Core - 55% complete</t>
+          <t>Platform / Core - 60% complete</t>
         </is>
       </c>
     </row>
@@ -1646,17 +1911,17 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>ai_usage_ledger - append-only, one row per attempt, with model alias, prompt version, sensitivity, policy version, cost and outcome. Migration 021.</t>
+          <t>ai_usage_ledger, written by recordUsage() in ai/store.ts from jobs.ts recordJobResult - one row per ATTEMPT, plus a 'rejected' row when policy refuses at enqueue.</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>No writer: ai_usage_ledger has no INSERT site in src/. Table is live; nothing records to it.</t>
+          <t>ai-cost.ts still reads ai_job, so that report under-counts until it is repointed at the ledger. Budget checks already read the ledger.</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -1683,17 +1948,17 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>ai/policy.ts + ai_tenant_policy - deployment modes, per-classification boundaries, eligibility before scoring, tenant may narrow never widen. 47 tests.</t>
+          <t>ai/policy.ts + ai_tenant_policy, loaded per tenant by ai/store.ts and consulted by ai/govern.ts on every enqueueJob. Decision and policy_version recorded on the ledger.</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Not imported by any file. Policy that nothing consults does not constrain anything.</t>
+          <t>Enforcement is behind AI_POLICY_ENFORCE, unset in production, so a refusal is recorded rather than applied. Deliberate: unclassified data defaults to confidential, which saas mode forbids sending to an external model - turning it on today would stop every job until data is classified or the tenant policy is widened.</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
@@ -1720,17 +1985,17 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>ai/registry.ts + ai_model_registry - aliases, capabilities, rate cards, loud failure on unknown alias. 37 tests with cache.</t>
+          <t>ai/registry.ts + ai_model_registry, seeded by migration 022 with the five aliases; jobs.ts resolves tier -&gt; alias -&gt; provider model from the table and stores the resolved model on ai_job.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>The four files naming concrete models are not yet migrated to aliases.</t>
+          <t>Swapping a model is now an UPDATE on the table, but MODEL_ROUTING / MODEL_STANDARD / MODEL_DEEP remain as the fallback when the registry has no row.</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
@@ -1794,17 +2059,17 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>ai/budget.ts - estimate before running, tenant limits, clamping, remedies in the order section 21 recommends. 47 tests with policy.</t>
+          <t>ai/budget.ts, called by ai/govern.ts before enqueue: estimates from the registry rate card, then checkLimits against spend read from the usage ledger.</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Not imported by any file. A budget nothing checks caps nothing.</t>
+          <t>Estimates input tokens from the inlined artifacts at 4 chars/token. Good enough to catch an order-of-magnitude overrun; not a substitute for count_tokens.</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
@@ -2716,7 +2981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3301,7 +3566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3594,6 +3859,407 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Preckon - completion against v1 scope (the P0 set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>The Module Dashboard measures against the blueprints as written - the full scope those documents describe and themselves budget a large team for. This sheet measures the same rows against the P0 subset only: what was committed for v1. Same evidence, same grading, different denominator. Read the caveat column before quoting a number - three modules have very few P0 features, so a high percentage there means 'the little that was committed is done', not 'the module is finished'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>P0 features</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>% of v1 scope</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Progress</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>Caveat</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>TenderLogix</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>█████████████████░░░</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>6 P0 features. Requirements-with-citation and the compliance matrix are the ones still partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>DocLogix</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>██████████████████░░</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>9 P0 features, built out on 20 Aug. Most of it is reachable only through the API; OCR is absent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>DrawLogix</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>████████████████████</t>
+        </is>
+      </c>
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>All 5 P0 features complete. Recognition, IFC and clash are P1/P2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>QuantLogix</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G8" s="27" t="inlineStr">
+        <is>
+          <t>██████████████░░░░░░</t>
+        </is>
+      </c>
+      <c r="H8" s="29" t="inlineStr">
+        <is>
+          <t>5 P0 features. source_region exists; takeoff still has to write the regions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>CostLogix</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>████████████████████</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>Only 1 feature was marked P0. Everything after award - budget, commitments, forecast, EVM - is P1/P2 and unbuilt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>ScheduleLogix</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>████████████████████</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>Only 3 features are P0. The migration-first mission (P6 import, calendars, baselines) sits outside the P0 set and is unbuilt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>ProcureLogix</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>████████████████████</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>Only 1 feature is P0. RFQ, quotes and commitments are P1/P2 and not started.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>NarrativeLogix</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr"/>
+      <c r="H12" s="29" t="inlineStr">
+        <is>
+          <t>No P0 features defined, so there is no v1 commitment to measure. Blueprint view: 83%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Platform-Core</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>████████████░░░░░░░░</t>
+        </is>
+      </c>
+      <c r="H13" s="29" t="inlineStr">
+        <is>
+          <t>24 P0 features - the broadest v1 commitment in the product. SSO, MFA, backups, staging, branch protection and CI are the P0 gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>TOTAL (v1 scope)</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="n">
+        <v>54</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>38</v>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="31" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="G14" s="30" t="inlineStr">
+        <is>
+          <t>███████████████░░░░░</t>
+        </is>
+      </c>
+      <c r="H14" s="32" t="inlineStr">
+        <is>
+          <t>Against the full blueprint scope the same evidence reads 52.7% across 132 features.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4339,7 +5005,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4974,7 +5640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5646,7 +6312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6133,7 +6799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6509,7 +7175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7144,7 +7810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7444,195 +8110,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>NarrativeLogix - 83% complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Technical narrative and proposal writing.  3 features audited: 2 done, 1 partial, 0 missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Evidence in code / DB</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Gap - what is still needed</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Effort</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Drafting</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Technical narrative sections</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>narrative_section artifact type; agent.narrative; workflow.narrativelogix; surfaces/narrative.tsx.</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Export</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Narrative export to markdown</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>narrative/export.md endpoint.</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Narrative grounded in project evidence</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Sections reference artifacts.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>No retrieval layer, so grounding is limited to what is passed in the envelope.</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:G7"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Preckon_Module_Completion.xlsx
+++ b/Preckon_Module_Completion.xlsx
@@ -194,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -285,6 +285,24 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -799,7 +817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every feature verified against the codebase and the deployed database on 20 Aug 2026, after the 14:45 deploy (app and worker rebuilt, 22 migrations applied, model registry seeded). Weighted: Done 1.0, Partial 0.5, Scaffolded 0.25, Missing 0. This revision moves four Platform features to Done because the AI governance layer is now called on the dispatch path rather than merely existing: ai/govern.ts is imported by jobs.ts, decisions are written to ai_usage_ledger, and 11 tests cover the decision matrix. Response cache and prompt registry stay Partial - still no caller.</t>
+          <t>Every feature verified against the codebase and the deployed database on 20 Aug 2026, after the 16:05 deploy (app and worker rebuilt, 23 migrations applied, procurement tables live). Weighted: Done 1.0, Partial 0.5, Scaffolded 0.25, Missing 0. This revision adds twelve features built the same day - ProcureLogix RFQ/quotes/coverage, CostLogix rates/scenarios/waterfall/cashflow, ScheduleLogix calendars/baselines/progress/health, TenderLogix scope-gaps/clarifications - each a domain module with tests, the basis on which numbering.ts and retention.ts were already graded Done. 841 tests pass; the suite grew by 77.</t>
         </is>
       </c>
     </row>
@@ -865,20 +883,20 @@
         <v>18</v>
       </c>
       <c r="D5" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="G5" s="7" t="n">
-        <v>0.472</v>
+        <v>0.556</v>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>█████████░░░░░░░░░░░</t>
+          <t>███████████░░░░░░░░░</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1013,20 +1031,20 @@
         <v>8</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.188</v>
+        <v>0.625</v>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>████░░░░░░░░░░░░░░░░</t>
+          <t>████████████░░░░░░░░</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1050,20 +1068,20 @@
         <v>15</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>0.267</v>
+        <v>0.533</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>█████░░░░░░░░░░░░░░░</t>
+          <t>███████████░░░░░░░░░</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1087,20 +1105,20 @@
         <v>6</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.167</v>
+        <v>0.667</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>███░░░░░░░░░░░░░░░░░</t>
+          <t>█████████████░░░░░░░</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1198,20 +1216,20 @@
         <v>132</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.527</v>
+        <v>0.617</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>███████████░░░░░░░░░</t>
+          <t>████████████░░░░░░░░</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -3934,27 +3952,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>TenderLogix</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="34" t="n">
         <v>0.833</v>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t>█████████████████░░░</t>
         </is>
@@ -3966,27 +3984,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>DocLogix</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="34" t="n">
         <v>0.889</v>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="33" t="inlineStr">
         <is>
           <t>██████████████████░░</t>
         </is>
@@ -3998,27 +4016,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>DrawLogix</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="33" t="inlineStr">
         <is>
           <t>████████████████████</t>
         </is>
@@ -4030,27 +4048,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>QuantLogix</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="36" t="n">
         <v>0.7</v>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>██████████████░░░░░░</t>
         </is>
@@ -4062,27 +4080,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>CostLogix</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>████████████████████</t>
         </is>
@@ -4094,27 +4112,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>ScheduleLogix</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G10" s="33" t="inlineStr">
         <is>
           <t>████████████████████</t>
         </is>
@@ -4126,27 +4144,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>ProcureLogix</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t>████████████████████</t>
         </is>
@@ -4158,29 +4176,29 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>NarrativeLogix</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
+      <c r="B12" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="28" t="n">
+      <c r="E12" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G12" s="27" t="inlineStr"/>
+      <c r="G12" s="35" t="inlineStr"/>
       <c r="H12" s="29" t="inlineStr">
         <is>
           <t>No P0 features defined, so there is no v1 commitment to measure. Blueprint view: 83%.</t>
@@ -4188,27 +4206,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>Platform-Core</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n">
+      <c r="B13" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D13" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E13" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="36" t="n">
         <v>0.604</v>
       </c>
-      <c r="G13" s="27" t="inlineStr">
+      <c r="G13" s="35" t="inlineStr">
         <is>
           <t>████████████░░░░░░░░</t>
         </is>
@@ -4220,34 +4238,34 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>TOTAL (v1 scope)</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="38" t="n">
         <v>54</v>
       </c>
-      <c r="C14" s="31" t="n">
+      <c r="C14" s="38" t="n">
         <v>38</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="E14" s="31" t="n">
+      <c r="E14" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="F14" s="31" t="n">
+      <c r="F14" s="38" t="n">
         <v>0.759</v>
       </c>
-      <c r="G14" s="30" t="inlineStr">
+      <c r="G14" s="37" t="inlineStr">
         <is>
           <t>███████████████░░░░░</t>
         </is>
       </c>
       <c r="H14" s="32" t="inlineStr">
         <is>
-          <t>Against the full blueprint scope the same evidence reads 52.7% across 132 features.</t>
+          <t>Against the full blueprint scope the same evidence reads 61.7% across 132 features.</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4298,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TenderLogix - 47% complete</t>
+          <t>TenderLogix - 56% complete</t>
         </is>
       </c>
     </row>
@@ -4564,17 +4582,17 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>tender/scope.ts - walks requirements against priced scope, so a gap is findable at all. Detects unpriced requirements, the same discipline priced in two packages, scope priced against no package, and requirements met only by excluded scope. Rolls up by package, discipline or delivery route.</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Specified-but-unpriced, drawing-without-BOQ and duplicate-scope detection all absent.</t>
+          <t>Requirement-to-scope links must exist; it does not infer them from text.</t>
         </is>
       </c>
       <c r="F11" s="18" t="inlineStr">
@@ -4638,17 +4656,17 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>client_query artifact type; agent.clarification; workflow.clarificationloop.</t>
+          <t>tender/clarifications.ts - submission refused after the questions deadline with the honest alternative stated; 'answered' and 'carried into the bid' kept as separate states, and an answered-but-not-incorporated item outranks an unanswered one in the risk list. 12 tests with tender/scope.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>No Draft-Review-Approved-Submitted-Answered-Impact-Closed state machine; impact assessment not enforced before close.</t>
+          <t>No client-portal integration; answers are recorded by the bid team.</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
@@ -6820,7 +6838,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CostLogix - 19% complete</t>
+          <t>CostLogix - 62% complete</t>
         </is>
       </c>
     </row>
@@ -6882,17 +6900,17 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>library_entry table; library endpoints; cost_line artifact type; agent.cost.</t>
+          <t>cost/rates.ts - rates carry source, capture date and region; lookup precedence is project, then region, then strength of source (subcontract &gt; quotation &gt; historic &gt; published &gt; estimate), then recency. Staleness flagged; indexation reported separately from the captured rate.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>No structured rate book with build-ups, regions, currencies or effective dates.</t>
+          <t>No UI for curating the library yet; rates are supplied by the caller.</t>
         </is>
       </c>
       <c r="F5" s="18" t="inlineStr">
@@ -6956,17 +6974,17 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>cost/scenarios.ts - base/target/BAFO as ordered adjustments against one base rather than copies of the bill, so the delta between any two is answerable line by line with the reason attached.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>TenderLogix governs revisions and scenarios; none exist.</t>
+          <t>Scenarios are not yet persisted as their own rows.</t>
         </is>
       </c>
       <c r="F7" s="18" t="inlineStr">
@@ -6993,17 +7011,17 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>cost/waterfall.ts - markup-on-cost and margin-on-price are separate bases and the margin one is solved, not approximated. Fixed stages and excluded-from-base stages supported; stages sum exactly to the sell price.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>No preliminaries, overhead, escalation, contingency, risk allowance, profit or tax breakdown.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">
@@ -7104,17 +7122,17 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>cost/cashflow.ts - S-curve spread per activity, certified value less retention, payment lag, retention release; reports peak funding and the month it occurs. 21 tests across this module and the three above.</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Straight monthly buckets; no weekly granularity and no financing cost.</t>
         </is>
       </c>
       <c r="F11" s="19" t="inlineStr">
@@ -7196,7 +7214,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ScheduleLogix - 27% complete</t>
+          <t>ScheduleLogix - 53% complete</t>
         </is>
       </c>
     </row>
@@ -7406,17 +7424,17 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>programme/calendars.ts - Gulf (Sun-Thu) and western weeks as data, holidays, three-level nesting where a child may only remove working time. Lays CPM day-offsets onto real dates.</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>P0 in the ScheduleLogix matrix (SL-P6-009). CPM without calendars cannot reconcile with P6.</t>
+          <t>No per-shift or part-day calendars.</t>
         </is>
       </c>
       <c r="F9" s="18" t="inlineStr">
@@ -7554,17 +7572,17 @@
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>programme/baselines.ts - baselines frozen on capture; re-baselining stores a new version and REFUSES without a stated reason; variance measured against a named baseline, reporting added and removed activities as well as slippage.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>P0 (SL-P6-023, 024). No baseline compare or immutable published snapshots.</t>
+          <t>Variance is by dates; no resource or cost variance.</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
@@ -7591,17 +7609,17 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>programme/progress.ts - duration, physical and value-weighted earned percent computed separately at a data date; elapsed time never substitutes for physical progress; forecasts from achieved rate when no remaining duration is given.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>P0 (SL-P6-015, 017, 018).</t>
+          <t>Single data date per report; no progress history curve yet.</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
@@ -7702,17 +7720,17 @@
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>programme/health.ts - DCMA-style structural checks: dangling logic, negative float, high float, long durations, lags, leads, constrained dates, critical-path share. Weighted score, grade, and the offending activities named. 21 tests.</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>The structural half of DCMA-14; resource and actuals checks need loading data.</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
@@ -7831,7 +7849,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ProcureLogix - 17% complete</t>
+          <t>ProcureLogix - 67% complete</t>
         </is>
       </c>
     </row>
@@ -7930,17 +7948,17 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>procure/rfq.ts - draft/issued/closed/awarded states, reissue as a new revision, deadline extend-forward-only, decline handling; rfq + rfq_vendor + vendor tables (023). 23 tests.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>No vendor master, no RFQ documents, no issue tracking.</t>
+          <t>No vendor portal: responses are recorded by the buyer rather than entered by the vendor.</t>
         </is>
       </c>
       <c r="F6" s="18" t="inlineStr">
@@ -7967,17 +7985,17 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>procure/quotes.ts - like-for-like comparison. Gaps filled from the median of what other vendors charged, then the estimate; an unfillable gap makes the quote non-comparable rather than free. quote + quote_line tables (023).</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>No bid levelling or comparison grid.</t>
+          <t>No OCR of emailed quotes; lines are captured rather than parsed. Currencies are flagged, not converted.</t>
         </is>
       </c>
       <c r="F7" s="18" t="inlineStr">
@@ -8004,17 +8022,17 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>procure/coverage.ts - walks packages, not enquiries, so a package with no RFQ appears at all. Flags no_rfq, all_declined, single_source, thin_field, overdue, unawarded; sorted by severity then exposure.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Single source, expiry, scope exclusion and missing package flags absent.</t>
+          <t>Exposure uses the estimate value; it does not re-price the gap.</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">

--- a/Preckon_Module_Completion.xlsx
+++ b/Preckon_Module_Completion.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3330" yWindow="3330" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module Dashboard" sheetId="1" state="visible" r:id="rId1"/>
@@ -32,14 +31,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Platform-Core'!$A$4:$G$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'P0 Backlog'!$A$4:$F$20</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,24 +47,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0012303F"/>
+      <color rgb="FF12303F"/>
       <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="004A6572"/>
+      <color rgb="FF4A6572"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
@@ -75,32 +79,64 @@
     </font>
     <font>
       <name val="Consolas"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001A2E35"/>
+      <color rgb="FF1A2E35"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000B1B2B"/>
+      <color rgb="FF0B1B2B"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001B5E20"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00E65100"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B71C1C"/>
+    </font>
+    <font>
+      <color rgb="001B5E20"/>
+    </font>
+    <font>
+      <color rgb="00E65100"/>
+    </font>
+    <font>
+      <color rgb="00B71C1C"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B1B2B"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -109,7 +145,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0012303F"/>
+        <fgColor rgb="FF12303F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCDD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6572"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F5FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1B2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,37 +190,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFCDD2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004A6572"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E1F5FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000B1B2B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8FAF6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF3E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,40 +204,40 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CFD8DC"/>
+        <color rgb="FFCFD8DC"/>
       </left>
       <right style="thin">
-        <color rgb="00CFD8DC"/>
+        <color rgb="FFCFD8DC"/>
       </right>
       <top style="thin">
-        <color rgb="00CFD8DC"/>
+        <color rgb="FFCFD8DC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CFD8DC"/>
+        <color rgb="FFCFD8DC"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E3E8EF"/>
+        <color rgb="FFE3E8EF"/>
       </left>
       <right style="thin">
-        <color rgb="00E3E8EF"/>
+        <color rgb="FFE3E8EF"/>
       </right>
       <top style="thin">
-        <color rgb="00E3E8EF"/>
+        <color rgb="FFE3E8EF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E3E8EF"/>
+        <color rgb="FFE3E8EF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -251,57 +292,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -313,9 +305,80 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -396,27 +459,38 @@
       <tx>
         <rich>
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Completion by module</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
     </title>
     <plotArea>
+      <layout/>
       <barChart>
         <barDir val="bar"/>
         <grouping val="clustered"/>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Module Dashboard'!G4</f>
+              <f>'Module Dashboard'!$G$4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>% Complete</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -424,17 +498,87 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="1"/>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Module Dashboard'!$A$5:$A$13</f>
-            </numRef>
+              <strCache>
+                <ptCount val="9"/>
+                <pt idx="0">
+                  <v>TenderLogix</v>
+                </pt>
+                <pt idx="1">
+                  <v>DocLogix</v>
+                </pt>
+                <pt idx="2">
+                  <v>DrawLogix</v>
+                </pt>
+                <pt idx="3">
+                  <v>QuantLogix</v>
+                </pt>
+                <pt idx="4">
+                  <v>CostLogix</v>
+                </pt>
+                <pt idx="5">
+                  <v>ScheduleLogix</v>
+                </pt>
+                <pt idx="6">
+                  <v>ProcureLogix</v>
+                </pt>
+                <pt idx="7">
+                  <v>NarrativeLogix</v>
+                </pt>
+                <pt idx="8">
+                  <v>Platform / Core</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Module Dashboard'!$G$5:$G$13</f>
+              <numCache>
+                <formatCode>0%</formatCode>
+                <ptCount val="9"/>
+                <pt idx="0">
+                  <v>0.556</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.8</v>
+                </pt>
+                <pt idx="2">
+                  <v>0.594</v>
+                </pt>
+                <pt idx="3">
+                  <v>0.591</v>
+                </pt>
+                <pt idx="4">
+                  <v>0.625</v>
+                </pt>
+                <pt idx="5">
+                  <v>0.533</v>
+                </pt>
+                <pt idx="6">
+                  <v>0.667</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.833</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.6</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -444,41 +588,57 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="1"/>
         <axPos val="l"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="1"/>
+        <axPos val="b"/>
         <majorGridlines/>
         <title>
           <tx>
             <rich>
               <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
               <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="en-US"/>
                   <a:t>% complete</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
         </title>
+        <numFmt formatCode="0%" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
       </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -802,450 +962,500 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="72" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" style="25" min="1" max="1"/>
+    <col width="42" customWidth="1" style="25" min="2" max="2"/>
+    <col width="10" customWidth="1" style="25" min="3" max="3"/>
+    <col width="8" customWidth="1" style="25" min="4" max="4"/>
+    <col width="9" customWidth="1" style="25" min="5" max="5"/>
+    <col width="10" customWidth="1" style="25" min="6" max="6"/>
+    <col width="12" customWidth="1" style="25" min="7" max="7"/>
+    <col width="24" customWidth="1" style="25" min="8" max="8"/>
+    <col width="72" customWidth="1" style="25" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Preckon - completion by module</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Every feature verified against the codebase and the deployed database on 20 Aug 2026, after the 16:05 deploy (app and worker rebuilt, 23 migrations applied). Weighted: Done 1.0, Partial 0.5, Scaffolded 0.25, Missing 0. Each module's percentage is computed from its own sheet, and the P0 Backlog is generated from those same rows - so the dashboard, the detail and the backlog cannot disagree. 841 tests pass across 38 files.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>What it does</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>% Complete</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>Where it stands</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="44.1" customHeight="1" s="25">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TenderLogix</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Tender engineering and bid orchestration</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="32" t="n">
         <v>0.556</v>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="33" t="inlineStr">
         <is>
           <t>███████████░░░░░░░░░</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Lifecycle, bid decision and approval work end to end. Requirements-with-citation and the compliance matrix - the module's core promise - are only partly there.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="44.1" customHeight="1" s="25">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>DocLogix</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>CDE, document control and document intelligence</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="34" t="n">
         <v>0.8</v>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="35" t="inlineStr">
         <is>
           <t>████████████████░░░░</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Built out on 20 Aug from 23%. Register, numbering, revisions, transmittals, revision diff, retrieval, review, distribution and retention all work and are deployed. The honest limit: most of it is reachable only through the API, and OCR is absent.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="44.1" customHeight="1" s="25">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>DrawLogix</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Drawing, design, BIM and drawing intelligence</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="32" t="n">
         <v>0.594</v>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="33" t="inlineStr">
         <is>
           <t>████████████░░░░░░░░</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>The strongest module. Intake, viewer, takeoff, revision compare and the AI copilot all work. Recognition, IFC and clash are the gaps.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="44.1" customHeight="1" s="25">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>QuantLogix</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Takeoff, quantities and BOQ</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="32" t="n">
         <v>0.591</v>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="33" t="inlineStr">
         <is>
           <t>████████████░░░░░░░░</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Measurement, BOQ and reconciliation are solid. source_region now exists, so the headline click-a-quantity-see-the-drawing claim is unblocked at the data layer - takeoff still has to write the regions.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="44.1" customHeight="1" s="25">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>CostLogix</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Rates, estimating and commercial</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="32" t="n">
         <v>0.625</v>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>████████████░░░░░░░░</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Pricing works. Everything after award - budget, commitments, forecast, EVM - is not started.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="44.1" customHeight="1" s="25">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>ScheduleLogix</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Scheduling and project time intelligence</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="33" t="inlineStr">
         <is>
           <t>███████████░░░░░░░░░</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>A real deterministic CPM engine exists. The migration-first mission - P6 import, calendars, baselines - is entirely unbuilt.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="44.1" customHeight="1" s="25">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>ProcureLogix</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Packages, RFQs and procurement</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="33" t="inlineStr">
         <is>
           <t>█████████████░░░░░░░</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Package grouping works. RFQ, quotes and commitments are not started.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="44.1" customHeight="1" s="25">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>NarrativeLogix</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Technical narrative and proposal writing</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="34" t="n">
         <v>0.833</v>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="35" t="inlineStr">
         <is>
           <t>█████████████████░░░</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Small module, largely complete for what it claims.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="44.1" customHeight="1" s="25">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Identity, tenancy, audit, AI governance, operations</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="33" t="inlineStr">
         <is>
           <t>████████████░░░░░░░░</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Trust foundations are strong: audit chain, tenant isolation, durable jobs, provenance. The AI governance layer is now WIRED, not just written: policy, model registry, budgets and the per-attempt usage ledger are consulted and recorded on every enqueue, deployed and seeded on 20 Aug. Enforcement stays behind a flag because unclassified data defaults to confidential, which saas mode forbids sending externally. Response cache and prompt registry remain unwired; enterprise ops (SSO, MFA, backups, staging, CI) are the real gap.</t>
         </is>
       </c>
     </row>
     <row r="14"/>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="15" ht="39.95" customHeight="1" s="25">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>All modules</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="10" t="n">
         <v>132</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="36" t="n">
         <v>69</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="37" t="n">
         <v>25</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="38" t="n">
         <v>38</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="39" t="n">
         <v>0.617</v>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="40" t="inlineStr">
         <is>
           <t>████████████░░░░░░░░</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Against the blueprints as written. Every figure on this row is the sum of the module sheets, which are the detail behind it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>built, tested, deployed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>exists but incomplete (counts as half)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>not started (counts as zero)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Percentages use the same three: green at or above 80%, amber 50-79%, red below 50%.</t>
         </is>
       </c>
     </row>
@@ -1268,1542 +1478,1542 @@
   <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="25" min="1" max="1"/>
+    <col width="44" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="54" customWidth="1" style="25" min="4" max="4"/>
+    <col width="60" customWidth="1" style="25" min="5" max="5"/>
+    <col width="9" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Platform / Core - 60% complete</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Identity, tenancy, audit, AI governance, operations.  40 features audited: 19 done, 9 partial, 12 missing.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Evidence in code / DB</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Gap - what is still needed</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="25.5" customHeight="1" s="25">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Better Auth; account, session, user, verification tables; rate limit on sign-in.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>SSO (SAML / OIDC)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Enterprise deal blocker. Named in Complete Platform section 15.</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>MFA</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Only i18n strings exist; no implementation.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Enterprise deal blocker.</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>SCIM provisioning</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+    <row r="9" ht="25.5" customHeight="1" s="25">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Tenancy</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Multi-tenant isolation</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>tenant scoping on every query; tenancy.test.ts and tenant-scoping.test.ts (static analysis of every SQL statement).</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>MySQL has no RLS, so the app layer is the only line. The static-analysis test is the compensating control.</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25.5" customHeight="1" s="25">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Tenancy</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Tenant provisioning and custom domains</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>tenant_bootstrap, tenant_domain, tenant_invite; provisioning.ts, domains.ts; domain provision endpoints.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="25.5" customHeight="1" s="25">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>AuthZ</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>RBAC roles and permissions</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>tenant_role, tenant_permission, tenant_role_permission, user_role; iam.ts; 6 seeded roles.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>No attribute-based rules (per-package subcontractor access).</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25.5" customHeight="1" s="25">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Audit</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Tamper-evident audit chain</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>audit_event + audit_chain hash chain; /api/v1/audit and /audit/verify; chain.ts.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25.5" customHeight="1" s="25">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Provenance</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Artifact provenance and review queue</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>artifact, artifact_type, artifact_provenance with JSON-schema validation; confirm, reject and trace endpoints.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25.5" customHeight="1" s="25">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Workflow</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Workflow and run engine</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>workflow, workflow_run, workflow_run_step; run_deviation with approve and reject.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25.5" customHeight="1" s="25">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Jobs</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Durable AI job queue</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>ai_job with idempotency_key; job-queue.ts conditional-UPDATE claims, leases, backoff, reconciler. 21 tests.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="38.25" customHeight="1" s="25">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Jobs</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Per-attempt usage ledger</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>ai_usage_ledger, written by recordUsage() in ai/store.ts from jobs.ts recordJobResult - one row per ATTEMPT, plus a 'rejected' row when policy refuses at enqueue.</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>ai-cost.ts still reads ai_job, so that report under-counts until it is repointed at the ledger. Budget checks already read the ledger.</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="17" ht="63.75" customHeight="1" s="25">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>AI Gov</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Tenant AI policy and data sensitivity</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>ai/policy.ts + ai_tenant_policy, loaded per tenant by ai/store.ts and consulted by ai/govern.ts on every enqueueJob. Decision and policy_version recorded on the ledger.</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Enforcement is behind AI_POLICY_ENFORCE, unset in production, so a refusal is recorded rather than applied. Deliberate: unclassified data defaults to confidential, which saas mode forbids sending to an external model - turning it on today would stop every job until data is classified or the tenant policy is widened.</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+    <row r="18" ht="38.25" customHeight="1" s="25">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>AI Gov</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Model registry and aliases</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>ai/registry.ts + ai_model_registry, seeded by migration 022 with the five aliases; jobs.ts resolves tier -&gt; alias -&gt; provider model from the table and stores the resolved model on ai_job.</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Swapping a model is now an UPDATE on the table, but MODEL_ROUTING / MODEL_STANDARD / MODEL_DEEP remain as the fallback when the registry has no row.</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="19" ht="25.5" customHeight="1" s="25">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>AI Gov</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Prompt registry with versions</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>ai_prompt_version table with prompt_key, version, task_type, prefix hash and approval status.</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>The worker still reads its prompts from source; nothing populates the table yet.</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="20" ht="38.25" customHeight="1" s="25">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>AI Gov</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Budgets (token, cost, latency)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>ai/budget.ts, called by ai/govern.ts before enqueue: estimates from the registry rate card, then checkLimits against spend read from the usage ledger.</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Estimates input tokens from the inlined artifacts at 4 chars/token. Good enough to catch an order-of-magnitude overrun; not a substitute for count_tokens.</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+    <row r="21" ht="25.5" customHeight="1" s="25">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>AI Gov</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Response cache (exact, semantic, artifact)</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>ai/cache.ts + ai_response_cache - every answer-changing dimension in the key, scoped invalidation triggers. 37 tests.</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Keys and safety rules exist; nothing reads or writes the table yet.</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+    <row r="22" ht="25.5" customHeight="1" s="25">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>AI Gov</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Retrieval / RAG</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>retrieval.ts + index-store.ts write and search the chunk table; revision-aware, budget-packed. 34 tests.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Wired for DocLogix only. No embeddings generated, and the AI worker does not call it yet - so agents still answer from the envelope.</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Transactional outbox</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>event_outbox and usage_outbox tables.</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>No published event catalog or schema versioning.</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25.5" customHeight="1" s="25">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Observability</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Structured logging</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>log.ts - request ids, AsyncLocalStorage context, key-based redaction. 21 tests.</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Observability</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Metrics, tracing, dashboards</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>trace_id exists on ai_job but no OpenTelemetry.</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>No metrics endpoint, no dashboards, no alerting.</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>FinOps</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>AI cost reporting</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>ai-cost.ts; /api/v1/ai-cost. 19 tests.</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Built on under-counted data until the per-attempt ledger exists.</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="27" ht="25.5" customHeight="1" s="25">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Entitlements</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Modules, plans and entitlements</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>entitlement_snapshot, entitlements.ts, modules.ts; internal entitlements endpoint.</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="25.5" customHeight="1" s="25">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>UX</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Design system, WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>globals.css semantic tokens with computed contrast; design-system.test.ts (24 tests).</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="25.5" customHeight="1" s="25">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>UX</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Internationalisation EN / AR / FR with RTL</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>i18n/en, ar, fr; logical CSS properties; technical content not mirrored.</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>UX</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Light, dark and system themes</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Alias token layer; system bootstrap in layout.tsx.</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="51" customHeight="1" s="25">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Ops</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>CI running the test suite</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Six workflow files exist; none has ever executed (PAT lacks workflow scope).</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>426 tests and six quality gates run only on a developer machine. The publishing token also lacks `workflow` scope, so ci.yml cannot even be pushed to techsmeinc/preckon-tenant - the mirror carries no .github at all.</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F31" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Ops</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Automated backup and tested restore</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C32" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>An untested restore is not a backup.</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Ops</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Staging environment</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C33" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Production only.</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Changes are currently validated in production.</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Ops</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Branch protection and PR review</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C34" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>autosync commits directly to main.</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>No review gate on production code.</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+    <row r="35" ht="38.25" customHeight="1" s="25">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Ops</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>schema.sql / migration drift guard</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C35" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>schema-drift.test.ts - fails if a migration creates a table schema.sql does not declare. Found 5 tables drifted since migration 004 whose queries had never been tenant-checked.</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="25.5" customHeight="1" s="25">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Ops</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Repeatable deploy</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>deploy.ps1 - sha256-verified resumable upload, migrations, catalog seed gate, worker rebuild.</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Encryption at rest and key management</t>
         </is>
       </c>
-      <c r="C37" s="17" t="inlineStr">
+      <c r="C37" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Named in Complete Platform section 15.</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="F37" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Secrets management (Vault / KMS)</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C38" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Secrets in .env on the host.</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+    <row r="39" ht="25.5" customHeight="1" s="25">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Credential rotation</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
+      <c r="C39" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Outstanding from the earlier security review.</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Rotate everything ever committed; confirm the production DB password is not the default.</t>
         </is>
       </c>
-      <c r="F39" s="17" t="inlineStr">
+      <c r="F39" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+    <row r="40" ht="38.25" customHeight="1" s="25">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Upload validation and scan gating</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>upload-safety.ts - magic-number vs extension, blocked extensions, macro formats, path traversal, zip-bomb ratio, explicit scan states. 33 tests.</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Explicitly not an antivirus. A real scanner still needs to sit behind it, and the upload route does not call this yet.</t>
         </is>
       </c>
-      <c r="F40" s="18" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+    <row r="41" ht="25.5" customHeight="1" s="25">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Port hardening</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>3308, 4000 and 8081 bind to 127.0.0.1 and are externally closed.</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>3307 (MySQL), 11434 (Ollama, unauthenticated) and 5000 bind 0.0.0.0; only the provider firewall stops them.</t>
         </is>
       </c>
-      <c r="F41" s="17" t="inlineStr">
+      <c r="F41" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+    <row r="42" ht="25.5" customHeight="1" s="25">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Architecture Decision Records</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>docs/adr - 8 ADRs covering the stack conflict, queue, AI authority, aliases, policy, ledger, cache safety and isolation.</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>8 of the ~50 specified. The rest are unwritten, but the ones that settle live contradictions are done.</t>
         </is>
       </c>
-      <c r="F42" s="18" t="inlineStr">
+      <c r="F42" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Enterprise Integration Hub and connector SDK</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
+      <c r="C43" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>integrations.ts is stub-level.</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>No connector runtime, canonical mapping or reconciliation engine.</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+    <row r="44" ht="25.5" customHeight="1" s="25">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Cross-module knowledge graph</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>pcm_relationship with typed edges, source and confidence.</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>PCM-scoped only. No Doc-Draw-Quant-Cost-Schedule traversal, no lineage or downstream-impact APIs.</t>
         </is>
       </c>
-      <c r="F44" s="18" t="inlineStr">
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -2828,574 +3038,575 @@
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" style="25" min="1" max="1"/>
+    <col width="44" customWidth="1" style="25" min="2" max="2"/>
+    <col width="10" customWidth="1" style="25" min="3" max="3"/>
+    <col width="78" customWidth="1" style="25" min="4" max="4"/>
+    <col width="8" customWidth="1" style="25" min="5" max="5"/>
+    <col width="9" customWidth="1" style="25" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Everything marked P0 that is not Done, across all modules</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+    <row r="2" ht="44.1" customHeight="1" s="25">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Generated from the module sheets, not maintained by hand - an earlier version of this sheet listed 8 items while the sheets carried 16, and the ones it omitted were the operational blockers. Ordered: Missing before Partial, then by module.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>What is still needed</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+    <row r="5" ht="30" customHeight="1" s="25">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>DocLogix</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Screens for register, review, transmittals and search</t>
         </is>
       </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D5" s="40" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Everything built today is reachable only through the API. This is the honest limit on calling the module done.</t>
         </is>
       </c>
-      <c r="E5" s="41" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F5" s="41" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>SSO (SAML / OIDC)</t>
         </is>
       </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D6" s="40" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Enterprise deal blocker. Named in Complete Platform section 15.</t>
         </is>
       </c>
-      <c r="E6" s="41" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F6" s="41" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>MFA</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D7" s="40" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>Enterprise deal blocker.</t>
         </is>
       </c>
-      <c r="E7" s="41" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F7" s="41" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+    <row r="8" ht="45" customHeight="1" s="25">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>CI running the test suite</t>
         </is>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>426 tests and six quality gates run only on a developer machine. The publishing token also lacks `workflow` scope, so ci.yml cannot even be pushed to techsmeinc/preckon-tenant - the mirror carries no .github at all.</t>
         </is>
       </c>
-      <c r="E8" s="41" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="F8" s="41" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Automated backup and tested restore</t>
         </is>
       </c>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>An untested restore is not a backup.</t>
         </is>
       </c>
-      <c r="E9" s="41" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F9" s="41" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Staging environment</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D10" s="40" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>Changes are currently validated in production.</t>
         </is>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F10" s="41" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>Branch protection and PR review</t>
         </is>
       </c>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D11" s="40" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>No review gate on production code.</t>
         </is>
       </c>
-      <c r="E11" s="41" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="F11" s="41" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>Encryption at rest and key management</t>
         </is>
       </c>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D12" s="40" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Named in Complete Platform section 15.</t>
         </is>
       </c>
-      <c r="E12" s="41" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F12" s="41" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+    <row r="13" ht="30" customHeight="1" s="25">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>Credential rotation</t>
         </is>
       </c>
-      <c r="C13" s="41" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D13" s="40" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Rotate everything ever committed; confirm the production DB password is not the default.</t>
         </is>
       </c>
-      <c r="E13" s="41" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="F13" s="41" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+    <row r="14" ht="30" customHeight="1" s="25">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>QuantLogix</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>Click a quantity, highlight contributing objects</t>
         </is>
       </c>
-      <c r="C14" s="41" t="inlineStr">
+      <c r="C14" s="49" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D14" s="40" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>No longer blocked at the data layer. Needs takeoff to write regions and the editor to highlight them.</t>
         </is>
       </c>
-      <c r="E14" s="41" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F14" s="41" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+    <row r="15" ht="30" customHeight="1" s="25">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>Retrieval / RAG</t>
         </is>
       </c>
-      <c r="C15" s="41" t="inlineStr">
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D15" s="40" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>Wired for DocLogix only. No embeddings generated, and the AI worker does not call it yet - so agents still answer from the envelope.</t>
         </is>
       </c>
-      <c r="E15" s="41" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F15" s="41" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>AI cost reporting</t>
         </is>
       </c>
-      <c r="C16" s="41" t="inlineStr">
+      <c r="C16" s="50" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D16" s="40" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>Built on under-counted data until the per-attempt ledger exists.</t>
         </is>
       </c>
-      <c r="E16" s="41" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="F16" s="41" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="39" t="inlineStr">
+    <row r="17" ht="30" customHeight="1" s="25">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Platform / Core</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>Port hardening</t>
         </is>
       </c>
-      <c r="C17" s="41" t="inlineStr">
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D17" s="40" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>3307 (MySQL), 11434 (Ollama, unauthenticated) and 5000 bind 0.0.0.0; only the provider firewall stops them.</t>
         </is>
       </c>
-      <c r="E17" s="41" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="F17" s="41" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+    <row r="18" ht="30" customHeight="1" s="25">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>QuantLogix</t>
         </is>
       </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>BOQ line to source object trace</t>
         </is>
       </c>
-      <c r="C18" s="41" t="inlineStr">
+      <c r="C18" s="50" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D18" s="40" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>The anchor exists but QuantLogix does not write regions yet - takeoff must record the polygon it measured.</t>
         </is>
       </c>
-      <c r="E18" s="41" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F18" s="41" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="39" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="25">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>TenderLogix</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Requirements extraction with clause citation</t>
         </is>
       </c>
-      <c r="C19" s="41" t="inlineStr">
+      <c r="C19" s="50" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D19" s="40" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>Clauses are extracted but are not turned into tracked Requirement objects with owner, due date, response and status.</t>
         </is>
       </c>
-      <c r="E19" s="41" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F19" s="41" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+    <row r="20" ht="30" customHeight="1" s="25">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>TenderLogix</t>
         </is>
       </c>
-      <c r="B20" s="40" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Compliance matrix</t>
         </is>
       </c>
-      <c r="C20" s="41" t="inlineStr">
+      <c r="C20" s="50" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D20" s="40" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>No matrix view, no mandatory flag, no Requirement-Evidence-Response-Approval chain.</t>
         </is>
       </c>
-      <c r="E20" s="41" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="F20" s="41" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="42" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>16 open P0 features</t>
         </is>
@@ -3420,269 +3631,269 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" style="25" min="1" max="1"/>
+    <col width="14" customWidth="1" style="25" min="2" max="2"/>
+    <col width="110" customWidth="1" style="25" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>What exists - counted, not assumed</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Queried from the repository and the deployed production database.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Modules seeded</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>tenderlogix, drawlogix, doclogix, quantlogix, costlogix, schedulelogix, narrativelogix, procurelogix</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+    <row r="6" ht="25.5" customHeight="1" s="25">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Artifact types</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>bid_approval, bid_decision, boq_line, client_query, compliance_item, cost_line, document, drawing_index, drawing_measurement, narrative_section, procurement_package, proposal_doc, rfi, risk, schedule_activity, spec_clause, standard_violation, tender_summary</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+    <row r="7" ht="25.5" customHeight="1" s="25">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>AI agents</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>approval_prep, bid_qualification, boq, clarification, commercial, compliance, compliance_lead, construction_copilot, cost, document, drawing, knowledge, narrative, procurement, proposal, rfi, risk, schedule, specification, tender</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Workflows</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>One per module plus 6 TenderLogix sub-workflows</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+    <row r="9" ht="25.5" customHeight="1" s="25">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Database tables</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="18" t="n">
         <v>82</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Was 77 on 20 Aug. ProcureLogix added 5: vendor, rfq, rfq_vendor, quote, quote_line - all declared in schema.sql as well as the migration.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Migrations</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>021 AI governance, 022 model registry seed, 023 procurement. All re-runnable and applied to production.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>API routes</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Was 78. Seven new DocLogix endpoints plus search</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Module surfaces</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>boq, drawings, estimate, narrative, procurement, schedule, specs, tender, common, generic - none yet for the DocLogix register</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>841 passing</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>38 files. Was 753. Procurement added 23, cost 21, programme 21, tender scope and clarifications 12.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="14" ht="38.25" customHeight="1" s="25">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Deterministic engines</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>cpm, pcm/measure, boq/reconcile, cad/compare, cad/impact, standards, doc/numbering, doc/revision, doc/compare, doc/review, doc/retention, ai/govern, plus the 13 added on 20 Aug: procure rfq/quotes/coverage, cost waterfall/rates/scenarios/cashflow, programme calendars/baselines/progress/health, tender scope/clarifications.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Live sheets in production</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Average 8.1 MB, largest 37 MB - still the biggest user-facing performance issue</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Deployed versions</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>next 15.5.23</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>postcss 8.5.26 - verified inside the running container</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>CI runs</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Six workflow files exist; none has ever executed. 632 tests run only on a developer machine.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+    <row r="18" ht="25.5" customHeight="1" s="25">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>ADRs</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Of ~50 specified. Cover the three-way stack conflict, queue choice, AI authority, model aliases, tenant policy, usage ledger, cache safety and tenant isolation.</t>
         </is>
@@ -3706,728 +3917,728 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="25" min="1" max="1"/>
+    <col width="44" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="54" customWidth="1" style="25" min="4" max="4"/>
+    <col width="60" customWidth="1" style="25" min="5" max="5"/>
+    <col width="9" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>TenderLogix - 56% complete</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Tender engineering and bid orchestration.  18 features audited: 5 done, 7 partial, 6 missing.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Evidence in code / DB</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Gap - what is still needed</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="25.5" customHeight="1" s="25">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Lifecycle</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Tender workspace and lifecycle states</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>lifecycle.ts, pursuit.ts, project lifecycle endpoint; workflow.tenderlogix + 5 sub-workflows seeded.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.5" customHeight="1" s="25">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Lifecycle</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Bid / no-bid decision</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>bid_decision artifact type; agent.bid_qualification; workflow.bidqualification.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25.5" customHeight="1" s="25">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Lifecycle</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Bid approval gate</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>bid_approval artifact type; agent.approval_prep; bid.approve permission on Owner role.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Intake</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Tender document intake and summary</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>tender_summary artifact type; agent.tender; workflow.classify.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="25.5" customHeight="1" s="25">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Requirements</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Requirements extraction with clause citation</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>spec_clause artifact type + agent.specification extract normative clauses.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Clauses are extracted but are not turned into tracked Requirement objects with owner, due date, response and status.</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+    <row r="10" ht="25.5" customHeight="1" s="25">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Requirements</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Compliance matrix</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>compliance_item artifact type; agent.compliance and agent.compliance_lead.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>No matrix view, no mandatory flag, no Requirement-Evidence-Response-Approval chain.</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="11" ht="63.75" customHeight="1" s="25">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Scope breakdown and gap detection</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>tender/scope.ts - walks requirements against priced scope, so a gap is findable at all. Detects unpriced requirements, the same discipline priced in two packages, scope priced against no package, and requirements met only by excluded scope. Rolls up by package, discipline or delivery route.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Requirement-to-scope links must exist; it does not infer them from text.</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="12" ht="25.5" customHeight="1" s="25">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>BOQ</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Employer vs derived vs adopted quantity reconciliation</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>boq/reconcile.ts - 4 verdicts, proportional tolerance with absolute floor, override trail. 27 tests.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Logic complete but NOT yet surfaced in the BOQ screen.</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="13" ht="63.75" customHeight="1" s="25">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Clarifications</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Clarification lifecycle</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>tender/clarifications.ts - submission refused after the questions deadline with the honest alternative stated; 'answered' and 'carried into the bid' kept as separate states, and an answered-but-not-incorporated item outranks an unanswered one in the risk list. 12 tests with tender/scope.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>No client-portal integration; answers are recorded by the bid team.</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="14" ht="25.5" customHeight="1" s="25">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Addenda</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Addendum intelligence and impact</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Unincorporated mandatory addendum must be a hard submission blocker. Not modelled at all.</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="15" ht="25.5" customHeight="1" s="25">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Risk register and commercial positions</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>risk artifact type; agent.risk; agent.commercial; workflow.riskreview.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>No assumptions/qualifications/exclusions register, no risk-adjusted margin.</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="16" ht="25.5" customHeight="1" s="25">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Bid strategy and scenarios</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Target/minimum margin, walk-away conditions, competitor assumptions absent.</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="17" ht="25.5" customHeight="1" s="25">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Submission</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Submission readiness score</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>submission.ts; lifecycle gates.</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Weighted readiness exists; the separate HARD GATE (blockers) is not implemented.</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+    <row r="18" ht="25.5" customHeight="1" s="25">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Submission</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Submission builder and manifest</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>proposal_doc artifact type; agent.proposal; workflow.bidassembly.</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>No manifest validation (revision, signature, naming, format, addendum acknowledgement); no revision freeze at submission.</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>War Room</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Tender War Room cockpit</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>surfaces/tender.tsx; project dashboards.</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>No countdown, readiness tiles, blocker list or AI brief.</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Negotiation</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Negotiation / BAFO revisions</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Award</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Award / loss capture and win-loss analytics</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Handover</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Bid-to-project handover</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Award should transfer to downstream modules with no re-keying.</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -4452,617 +4663,617 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="25" min="1" max="1"/>
+    <col width="44" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="54" customWidth="1" style="25" min="4" max="4"/>
+    <col width="60" customWidth="1" style="25" min="5" max="5"/>
+    <col width="9" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>DocLogix - 80% complete</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>CDE, document control and document intelligence.  15 features audited: 11 done, 2 partial, 2 missing.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Evidence in code / DB</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Gap - what is still needed</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="25.5" customHeight="1" s="25">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>File storage and binary versioning</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>file + file_page; document_revision.file_version bumps when the file is replaced without the revision changing.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38.25" customHeight="1" s="25">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Register</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Intelligent document register (35+ controlled fields)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>document_register - number, title, type, discipline, originator, volume, level, zone, package, confidentiality, status, retention, required_by. Registers before a file exists.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>API only - no register screen yet.</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+    <row r="7" ht="38.25" customHeight="1" s="25">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Numbering</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Document numbering engine</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>numbering.ts - schemes as data, segment validation, reserved ranges, sequence allocation, legacy adoption. Duplicates blocked by a unique index, not an app check that races. 33 tests.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38.25" customHeight="1" s="25">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Revisions</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Formal revision vs file version</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>revision.ts - alpha/numeric/ISO 19650, I and O skipped, C outranks P, supersession planned then applied atomically. 32 tests.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38.25" customHeight="1" s="25">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Revisions</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Revision intelligence (change classification)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>compare.ts - deterministic LCS diff over extracted text, classified as dimension/requirement/commercial/reference/note, significant-first review order. 28 tests.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Text only. Drawing-geometry diff is cad/compare.ts; the two are not yet joined into one report.</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+    <row r="10" ht="25.5" customHeight="1" s="25">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Workflow</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Configurable document workflow</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>document_review with stage, min_approvals, due_at; contractual response codes; issue gate. 44 tests with review.ts.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>No escalation, no reminders, no conditional branching. The SLA date exists and nothing acts on it.</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="11" ht="38.25" customHeight="1" s="25">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Review and approval workspace</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>document_review + document_review_assignee + document_comment; comments pinned to a source_region, threaded, blocking flag; decision log.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Backend complete, no UI. A reviewer cannot reach any of it without an API client.</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="12" ht="25.5" customHeight="1" s="25">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Transmittals</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Transmittal management</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>transmittal + item + recipient; carries revisions not documents; sending freezes; acknowledgements; recall never deletes. 35 tests.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>API only - no transmittal screen.</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Extraction</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Specification clause extraction</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>spec_clause artifact type; agent.specification; surfaces/specs.tsx.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25.5" customHeight="1" s="25">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Extraction</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>OCR for scanned documents</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>CAD extraction handles drawings only.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>No OCR for scanned PDFs, Office formats, email or images. Anything not already text-extracted is invisible to search.</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="15" ht="38.25" customHeight="1" s="25">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Semantic / natural-language project search</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>retrieval.ts + index-store.ts - meaning-based chunking, hybrid ranking, budget packing, revision-aware. The chunk table finally has a writer. 34 tests.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>No embeddings generated yet, so ranking is lexical plus identifier matching. The column and the cosine function are ready for them.</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="16" ht="25.5" customHeight="1" s="25">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Provenance</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Document-region provenance anchor</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>source_region - page, polygon, text range or model object, cited by entity_type/entity_id, with method and confidence.</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="25.5" customHeight="1" s="25">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Distribution</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Distribution lists and controlled issue</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>distribution_list + distribution_member with to/cc, applies_to filters for when a list is offered.</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="38.25" customHeight="1" s="25">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Retention categories and legal hold</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>retention.ts - hold outranks retention including expired retention; live references block; no policy is not permission. Nothing deletes, it answers whether deletion is permitted.</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25.5" customHeight="1" s="25">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Screens for register, review, transmittals and search</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>surfaces/drawings.tsx still renders the old file list.</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Everything built today is reachable only through the API. This is the honest limit on calling the module done.</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -5087,654 +5298,654 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="25" min="1" max="1"/>
+    <col width="44" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="54" customWidth="1" style="25" min="4" max="4"/>
+    <col width="60" customWidth="1" style="25" min="5" max="5"/>
+    <col width="9" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>DrawLogix - 59% complete</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Drawing, design, BIM and drawing intelligence.  16 features audited: 7 done, 5 partial, 4 missing.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Evidence in code / DB</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Gap - what is still needed</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="25.5" customHeight="1" s="25">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Intake</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>DWG / DXF / PDF intake</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>cad_extraction, file_page; Python sidecar with LibreDWG dwg2dxf; SVG render pipeline.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.5" customHeight="1" s="25">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Intake</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>IFC import and export</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>IFC is the open-BIM requirement named in three documents. No import or export at all.</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Viewer</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Drawing viewer with pan, zoom, layers</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>cad/editor.tsx, cad/viewport.tsx; 31 sheets live in production.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25.5" customHeight="1" s="25">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Recognition</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Symbol and object recognition to PCM candidates</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Extraction produces geometry and text, not classified construction objects.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>No recognition of walls, doors, windows, columns or rooms with confidence and a verification queue.</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Authoring</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>2D drafting and editing</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>cad/editor.tsx with measure, iso views, roundtrip to DXF.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>No trim/extend/offset/fillet/array; no hatch or leader tooling.</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Authoring</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>3D / BIM authoring</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>bim/studio.tsx, bim/model.ts, bim/iso.tsx.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>No true parametric BIM authoring; no slabs, roofs, stairs, curtain walls.</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="11" ht="38.25" customHeight="1" s="25">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Commands</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Deterministic command set</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>bim/commands.ts, cad/tools.ts; generic ToolRegistry with propose and apply. 108 tests across registry, tools and documentation.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Missing CreateSlab, Beam, Grid, Pipe, Duct, CreateView, CreateSheet, GenerateSchedule.</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="12" ht="25.5" customHeight="1" s="25">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>AI Design Copilot with execution modes</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>bim/agent2.ts, cad/agent.ts, cad/assistant route; discover-read-resolve-propose-review-apply-audit.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Matches the blueprint execution-mode model closely. The strongest AI surface in the product.</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25.5" customHeight="1" s="25">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Authored tools (user-defined automation)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>bim/authoring.ts, bim_authored_tool table, authoring-panel.tsx; steps are data, never code.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25.5" customHeight="1" s="25">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Revisions</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Revision comparison and impact</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>cad/compare.ts (content matching, adaptive tolerance) and cad/impact.ts. 39 tests.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25.5" customHeight="1" s="25">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Sheets, tags, dimensions</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>bim/sheets.tsx, bim/documentation.ts. 29 tests.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>No live schedules as PCM projections, no revision clouds, no sheet sets or issue packages.</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Coordination</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Clash and clearance detection</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>No model federation, no clash workflow.</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="17" ht="25.5" customHeight="1" s="25">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Components</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Smart components and families</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>library_entry table exists for reusable content.</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>No parametric component definitions with parameters, connectors, constraints or quantity rules.</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+    <row r="18" ht="25.5" customHeight="1" s="25">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Takeoff</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Drawing-to-quantity measurement</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>bim/takeoff.ts, cad/measure.ts, drawing_measurement artifact type with source_layers.</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25.5" customHeight="1" s="25">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Standards and rule validation</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>standards.ts, validate.ts; standard_violation artifact type; validate and violations endpoints.</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="25.5" customHeight="1" s="25">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Desktop</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Desktop Studio client</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Electron shell; desktop.ts, desktopBuilds.ts, bundles.ts; signed installers served from /desktop.</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>No native geometry runtime, no local PCM cache, no GPU renderer, no offline working package.</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -5759,469 +5970,469 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="25" min="1" max="1"/>
+    <col width="44" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="54" customWidth="1" style="25" min="4" max="4"/>
+    <col width="60" customWidth="1" style="25" min="5" max="5"/>
+    <col width="9" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>QuantLogix - 59% complete</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Takeoff, quantities and BOQ.  11 features audited: 5 done, 3 partial, 3 missing.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Evidence in code / DB</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Gap - what is still needed</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="25.5" customHeight="1" s="25">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Measurement engine</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>pcm/measure.ts, pcm/units.ts; drawing_measurement artifact type.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.5" customHeight="1" s="25">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Measurement</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Configurable measurement rules</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Measurement logic is in code, not data.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>No measurement_rule table, no versioned rule expressions, no standard references (NRM, POMI, CESMM).</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+    <row r="7" ht="25.5" customHeight="1" s="25">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>BOQ</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>BOQ generation from measurements</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>boq_line artifact type; agent.boq; workflow.quantlogix; surfaces/boq.tsx.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>BOQ</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>BOQ export (csv, xlsx)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>boq/export.csv and boq/export.xlsx endpoints; xlsx-brand.ts.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>BOQ</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>BOQ roster and rate application</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>boq/roster and boq/rate endpoints; boq/pipeline.tsx.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25.5" customHeight="1" s="25">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Reconciliation</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Multi-source quantity reconciliation</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>boq/reconcile.ts - modelled vs measured vs manual, 4 verdicts, override trail. 27 tests.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Not yet wired into the BOQ surface, so estimators cannot see disputes.</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="11" ht="25.5" customHeight="1" s="25">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Traceability</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>BOQ line to source object trace</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>pcm_boq_map, pcm_quantity, artifact_provenance, trace endpoints; source_region now exists and is deployed.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>The anchor exists but QuantLogix does not write regions yet - takeoff must record the polygon it measured.</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="12" ht="25.5" customHeight="1" s="25">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Traceability</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Click a quantity, highlight contributing objects</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>source_region table deployed 20 Aug; regionsFor() reads the evidence behind any entity.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>No longer blocked at the data layer. Needs takeoff to write regions and the editor to highlight them.</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="13" ht="25.5" customHeight="1" s="25">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Quantity dirty propagation and remeasure</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>pcm_quantity has a status column; cad/impact.ts identifies affected measurements.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Dirty-mark, queue, recompute pipeline is not wired end to end. Stale quantities can be displayed as current.</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>BOQ delta between revisions</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>cad/compare.ts produces the geometry delta.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>No BOQ-level delta report or baseline preservation.</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Assemblies</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Assemblies and composite items</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -6246,358 +6457,358 @@
   <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="25" min="1" max="1"/>
+    <col width="44" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="54" customWidth="1" style="25" min="4" max="4"/>
+    <col width="60" customWidth="1" style="25" min="5" max="5"/>
+    <col width="9" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>CostLogix - 62% complete</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Rates, estimating and commercial.  8 features audited: 1 done, 1 partial, 6 missing.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Evidence in code / DB</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Gap - what is still needed</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="63.75" customHeight="1" s="25">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Rates</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Rate library</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>cost/rates.ts - rates carry source, capture date and region; lookup precedence is project, then region, then strength of source (subcontract &gt; quotation &gt; historic &gt; published &gt; estimate), then recency. Staleness flagged; indexation reported separately from the captured rate.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>No UI for curating the library yet; rates are supplied by the caller.</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+    <row r="6" ht="25.5" customHeight="1" s="25">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Estimate</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Estimate generation and pricing</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>cost_line artifact type; agent.cost; workflow.costlogix; surfaces/estimate.tsx.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1" s="25">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Estimate</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimate scenarios (base, target, BAFO)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>cost/scenarios.ts - base/target/BAFO as ordered adjustments against one base rather than copies of the bill, so the delta between any two is answerable line by line with the reason attached.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Scenarios are not yet persisted as their own rows.</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+    <row r="8" ht="51" customHeight="1" s="25">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Margin waterfall and markups</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>cost/waterfall.ts - markup-on-cost and margin-on-price are separate bases and the margin one is solved, not approximated. Fixed stages and excluded-from-base stages supported; stages sum exactly to the sell price.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Budget, commitments, forecast</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Cost control after award is not started.</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>EVM</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Earned value (PV, EV, AC, SPI, CPI)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Requires schedule and cost integration.</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="11" ht="51" customHeight="1" s="25">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Cashflow</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Cash flow and S-curves</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>cost/cashflow.ts - S-curve spread per activity, certified value less retention, payment lag, retention release; reports peak funding and the month it occurs. 21 tests across this module and the three above.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Straight monthly buckets; no weekly granularity and no financing cost.</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Change</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Variation and change pricing</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>No ChangeLogix module exists.</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -6622,617 +6833,617 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="25" min="1" max="1"/>
+    <col width="44" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="54" customWidth="1" style="25" min="4" max="4"/>
+    <col width="60" customWidth="1" style="25" min="5" max="5"/>
+    <col width="9" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>ScheduleLogix - 53% complete</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Scheduling and project time intelligence.  15 features audited: 4 done, 0 partial, 11 missing.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Evidence in code / DB</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Gap - what is still needed</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="25.5" customHeight="1" s="25">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Engine</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Deterministic CPM engine</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>cpm.ts - forward and backward pass, FS/SS/FF/SF with lag, total float, critical path.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Genuinely deterministic and the AI is kept out of the arithmetic, exactly as the blueprint requires.</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.5" customHeight="1" s="25">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Activities and programme storage</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>project_programme table; schedule_activity artifact type; agent.schedule; workflow.schedulelogix.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25.5" customHeight="1" s="25">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Gantt and activity grid</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>programme/gantt.tsx; surfaces/schedule.tsx; programme endpoints.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>No frozen columns, bulk edit, saved layouts or network diagram.</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Export</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Programme export</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>programme/export.xlsx.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38.25" customHeight="1" s="25">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Calendars</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Global, project and resource calendars</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>programme/calendars.ts - Gulf (Sun-Thu) and western weeks as data, holidays, three-level nesting where a child may only remove working time. Lays CPM day-offsets onto real dates.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>No per-shift or part-day calendars.</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+    <row r="10" ht="25.5" customHeight="1" s="25">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>P6 XER import</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>RELEASE-BLOCKING (SL-P6-001). The module's stated mission is migration-first.</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>P6 XML import</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>RELEASE-BLOCKING (SL-P6-002).</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="12" ht="25.5" customHeight="1" s="25">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Reconciliation and migration confidence score</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Appendix B requires a signed-off reconciliation package, not an Import Successful message.</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="13" ht="51" customHeight="1" s="25">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Baselines</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Baselines and schedule versions</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>programme/baselines.ts - baselines frozen on capture; re-baselining stores a new version and REFUSES without a stated reason; variance measured against a named baseline, reporting added and removed activities as well as slippage.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Variance is by dates; no resource or cost variance.</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="14" ht="51" customHeight="1" s="25">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Progress, data date, percent complete</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>programme/progress.ts - duration, physical and value-weighted earned percent computed separately at a data date; elapsed time never substitutes for physical progress; forecasts from achieved rate when no remaining duration is given.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Single data date per report; no progress history curve yet.</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Resources</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Resources, roles, histogram, levelling</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>P1 tier (SL-P6-025, 033, 034).</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="16" ht="25.5" customHeight="1" s="25">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Look-ahead</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Look-ahead and work readiness</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Named differentiator; depends on connected procurement and drawing data.</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="17" ht="51" customHeight="1" s="25">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Intelligence</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Schedule health scoring</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>programme/health.ts - DCMA-style structural checks: dangling logic, negative float, high float, long durations, lags, leads, constrained dates, critical-path share. Weighted score, grade, and the offending activities named. 21 tests.</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>The structural half of DCMA-14; resource and actuals checks need loading data.</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Intelligence</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Delay intelligence and recovery scenarios</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Named the key differentiator in section 30.</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Intelligence</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>What-if sandbox</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -7257,284 +7468,284 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="25" min="1" max="1"/>
+    <col width="44" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="54" customWidth="1" style="25" min="4" max="4"/>
+    <col width="60" customWidth="1" style="25" min="5" max="5"/>
+    <col width="9" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>ProcureLogix - 67% complete</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Packages, RFQs and procurement.  6 features audited: 1 done, 0 partial, 5 missing.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Evidence in code / DB</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Gap - what is still needed</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="25.5" customHeight="1" s="25">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Packages</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>RFQ package grouping by trade and lead time</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>procurement_package artifact type; agent.procurement; workflow.procurelogix; surfaces/procurement.tsx.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38.25" customHeight="1" s="25">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>RFQ</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>RFQ issue and vendor management</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>procure/rfq.ts - draft/issued/closed/awarded states, reissue as a new revision, deadline extend-forward-only, decline handling; rfq + rfq_vendor + vendor tables (023). 23 tests.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>No vendor portal: responses are recorded by the buyer rather than entered by the vendor.</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+    <row r="7" ht="51" customHeight="1" s="25">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Quotes</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Quotation capture and comparison</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>procure/quotes.ts - like-for-like comparison. Gaps filled from the median of what other vendors charged, then the estimate; an unfillable gap makes the quote non-comparable rather than free. quote + quote_line tables (023).</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>No OCR of emailed quotes; lines are captured rather than parsed. Currencies are flagged, not converted.</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+    <row r="8" ht="51" customHeight="1" s="25">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>RFQ coverage and gap flags</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>procure/coverage.ts - walks packages, not enquiries, so a package with no RFQ appears at all. Flags no_rfq, all_declined, single_source, thin_field, overdue, unawarded; sorted by severity then exposure.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Exposure uses the estimate value; it does not re-price the gap.</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Commitments</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Purchase orders and commitments</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Delivery</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Delivery tracking and long-lead alerts</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="48" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -7559,173 +7770,173 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="25" min="1" max="1"/>
+    <col width="44" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="54" customWidth="1" style="25" min="4" max="4"/>
+    <col width="60" customWidth="1" style="25" min="5" max="5"/>
+    <col width="9" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>NarrativeLogix - 83% complete</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Technical narrative and proposal writing.  3 features audited: 2 done, 1 partial, 0 missing.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Evidence in code / DB</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Gap - what is still needed</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="25.5" customHeight="1" s="25">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Drafting</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Technical narrative sections</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>narrative_section artifact type; agent.narrative; workflow.narrativelogix; surfaces/narrative.tsx.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Export</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Narrative export to markdown</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>narrative/export.md endpoint.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25.5" customHeight="1" s="25">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Narrative grounded in project evidence</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Sections reference artifacts.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>No retrieval layer, so grounding is limited to what is passed in the envelope.</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/Preckon_Module_Completion.xlsx
+++ b/Preckon_Module_Completion.xlsx
@@ -1053,20 +1053,20 @@
         <v>18</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="32" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="H5" s="33" t="inlineStr">
-        <is>
-          <t>███████████░░░░░░░░░</t>
+        <v>3</v>
+      </c>
+      <c r="G5" s="34" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
+        <is>
+          <t>████████████████░░░░</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -1090,20 +1090,20 @@
         <v>15</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>0.8</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H6" s="35" t="inlineStr">
         <is>
-          <t>████████████████░░░░</t>
+          <t>███████████████████░</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1127,20 +1127,20 @@
         <v>16</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" s="30" t="n">
         <v>5</v>
       </c>
       <c r="F7" s="31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" s="32" t="n">
-        <v>0.594</v>
+        <v>0.719</v>
       </c>
       <c r="H7" s="33" t="inlineStr">
         <is>
-          <t>████████████░░░░░░░░</t>
+          <t>██████████████░░░░░░</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1164,20 +1164,20 @@
         <v>11</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="32" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="H8" s="33" t="inlineStr">
-        <is>
-          <t>████████████░░░░░░░░</t>
+        <v>2</v>
+      </c>
+      <c r="G8" s="34" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="H8" s="35" t="inlineStr">
+        <is>
+          <t>████████████████░░░░</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1201,20 +1201,20 @@
         <v>8</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" s="30" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="32" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>████████████░░░░░░░░</t>
+        <v>1</v>
+      </c>
+      <c r="G9" s="34" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H9" s="35" t="inlineStr">
+        <is>
+          <t>██████████████████░░</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1238,20 +1238,20 @@
         <v>15</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E10" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G10" s="32" t="n">
-        <v>0.533</v>
+        <v>0.767</v>
       </c>
       <c r="H10" s="33" t="inlineStr">
         <is>
-          <t>███████████░░░░░░░░░</t>
+          <t>███████████████░░░░░</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1275,20 +1275,20 @@
         <v>6</v>
       </c>
       <c r="D11" s="29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="H11" s="33" t="inlineStr">
-        <is>
-          <t>█████████████░░░░░░░</t>
+      <c r="G11" s="34" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="H11" s="35" t="inlineStr">
+        <is>
+          <t>██████████████████░░</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1387,20 +1387,20 @@
         <v>132</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F15" s="38" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G15" s="39" t="n">
-        <v>0.617</v>
+        <v>0.754</v>
       </c>
       <c r="H15" s="40" t="inlineStr">
         <is>
-          <t>████████████░░░░░░░░</t>
+          <t>███████████████░░░░░</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -1409,6 +1409,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="41" t="inlineStr">
         <is>
@@ -3604,7 +3605,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="23" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
     <row r="1" ht="24" customHeight="1" s="25">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>TenderLogix - 56% complete</t>
+          <t>TenderLogix - 81% complete</t>
         </is>
       </c>
     </row>
@@ -4137,19 +4137,19 @@
           <t>Requirements extraction with clause citation</t>
         </is>
       </c>
-      <c r="C9" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C9" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>spec_clause artifact type + agent.specification extract normative clauses.</t>
+          <t>tender/requirements.ts - a requirement cannot exist without document, clause and the QUOTED text; validateRequirement refuses a paraphrase, which is how requirements drift from what was asked. Supersession by addendum removes it from the live set. 30 tests across this module and the four below.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Clauses are extracted but are not turned into tracked Requirement objects with owner, due date, response and status.</t>
+          <t>Extraction itself is still the agent's job; this is the structure, citation rules and validation it must produce.</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -4174,19 +4174,19 @@
           <t>Compliance matrix</t>
         </is>
       </c>
-      <c r="C10" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>compliance_item artifact type; agent.compliance and agent.compliance_lead.</t>
+          <t>complianceMatrix() in tender/requirements.ts - ordered by the client's own reference numerically, so it reads alongside their document. Unanswered mandatory requirements and mandatory non-compliance are disqualifying; a compliance claim with no evidence reference and a deviation with no alternative offered are both flagged, because the first cannot be verified and the second reads as a refusal.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>No matrix view, no mandatory flag, no Requirement-Evidence-Response-Approval chain.</t>
+          <t>No export to the client's own matrix template yet.</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -4322,19 +4322,19 @@
           <t>Addendum intelligence and impact</t>
         </is>
       </c>
-      <c r="C14" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>tender/addenda.ts - maps each item to what it hits, classifies impact (a quantity change is critical; a withdrawal is significant), and tracks acknowledgement as state. An unacknowledged addendum is reported as bid-losing on its own, which is the cheapest way to lose. position() reads all addenda together, since a later one changes an earlier one.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Unincorporated mandatory addendum must be a hard submission blocker. Not modelled at all.</t>
+          <t>Addendum items are supplied structured; parsing an addendum PDF into items is the agent's job.</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -4359,19 +4359,19 @@
           <t>Risk register and commercial positions</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C15" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>risk artifact type; agent.risk; agent.commercial; workflow.riskreview.</t>
+          <t>tender/positions.ts - keeps priced and qualified apart, so a risk cannot be both charged for and disclaimed. Catches the three quiet failures: untreated risk, a risk both priced and excluded, and a qualification that never reached the submitted document - a position the contract will not know about.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>No assumptions/qualifications/exclusions register, no risk-adjusted margin.</t>
+          <t>Scoring is likelihood x impact; no Monte Carlo or correlated-risk modelling.</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -4433,19 +4433,19 @@
           <t>Submission readiness score</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>submission.ts; lifecycle gates.</t>
+          <t>tender/readiness.ts - weighted by consequence rather than counted. lib/submission.ts scored done-over-live, which weighs a missing bid bond the same as a missing org chart; disqualifying items are worth 10, scored 3, supporting 1, and a blocking set is returned rather than a percentage alone. Deadline-aware: complete but late is not submittable.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Weighted readiness exists; the separate HARD GATE (blockers) is not implemented.</t>
+          <t>Consequence rules are supplied per call; no per-client template library yet.</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
@@ -4470,19 +4470,19 @@
           <t>Submission builder and manifest</t>
         </is>
       </c>
-      <c r="C18" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>proposal_doc artifact type; agent.proposal; workflow.bidassembly.</t>
+          <t>manifest() in tender/readiness.ts - renders the envelope list in the CLIENT's stipulated order with format notes, and lists missing items marked NOT INCLUDED rather than omitting them, since a manifest showing only what exists reads as complete.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>No manifest validation (revision, signature, naming, format, addendum acknowledgement); no revision freeze at submission.</t>
+          <t>Renders the list; does not assemble or bind the PDF pack itself.</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
@@ -4581,19 +4581,19 @@
           <t>Award / loss capture and win-loss analytics</t>
         </is>
       </c>
-      <c r="C21" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C21" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>tender/outcome.ts - a loss without a reason is REFUSED, because the moment of recording is the only time anybody still knows why. Analytics separate narrow losses (a pricing problem) from wide ones (a positioning problem that sharpening will not fix), report hit rate by value as well as count, and say so when too many losses have no recorded reason for the analysis to be trusted.</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Win-loss data is per-tenant; no market benchmarking.</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="1" ht="24" customHeight="1" s="25">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>DocLogix - 80% complete</t>
+          <t>DocLogix - 93% complete</t>
         </is>
       </c>
     </row>
@@ -4920,19 +4920,19 @@
           <t>Configurable document workflow</t>
         </is>
       </c>
-      <c r="C10" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>document_review with stage, min_approvals, due_at; contractual response codes; issue gate. 44 tests with review.ts.</t>
+          <t>doc/workflow.ts - stages as data: parties, minApprovals, durations, sequential or parallel, appliesTo filters by doc type/discipline/confidentiality. validateWorkflow refuses a stage nobody is assigned to and one needing more approvals than it has reviewers. planStages/nextStages drive the chain; a rejection stops it. 15 tests.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>No escalation, no reminders, no conditional branching. The SLA date exists and nothing acts on it.</t>
+          <t>Workflows are code-level configuration; no screen to edit them, and the default consultant chain is what a project gets until one is supplied.</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -4957,19 +4957,19 @@
           <t>Review and approval workspace</t>
         </is>
       </c>
-      <c r="C11" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>document_review + document_review_assignee + document_comment; comments pinned to a source_region, threaded, blocking flag; decision log.</t>
+          <t>doc/review-store.ts + 2 routes (reviews, reviews/[rvid]) - open a cycle, record a party's decision, comment, and close on review.ts's own canComplete. Wired into the issue route: a revision under open or failed review returns 409 with the reason. Reviewable from the Register screen.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Backend complete, no UI. A reviewer cannot reach any of it without an API client.</t>
+          <t>Decisions are recorded by party name rather than by assigned user account; no email notification to reviewers.</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>No OCR for scanned PDFs, Office formats, email or images. Anything not already text-extracted is invisible to search.</t>
+          <t>Needs a real OCR engine, which is an infrastructure decision rather than a file to write: Tesseract into the cad sidecar, or a hosted API. Not graded Done because a pipeline with no engine behind it reads scanned drawings as empty, which is worse than refusing them.</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -5253,19 +5253,19 @@
           <t>Screens for register, review, transmittals and search</t>
         </is>
       </c>
-      <c r="C19" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C19" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>surfaces/drawings.tsx still renders the old file list.</t>
+          <t>doc/register-panel.tsx, mounted as a Register tab beside Intake on the documents page - register table with late-flagging, registration drawer driven by the scheme's own segments (422 shown per segment, no number burned), per-document drawer with revisions, send-for-review, decide, issue, and a transmittals table.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Everything built today is reachable only through the API. This is the honest limit on calling the module done.</t>
+          <t>One screen covering register, revisions, review and transmittals; distribution lists and retention still have no UI.</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -5310,7 +5310,7 @@
     <row r="1" ht="24" customHeight="1" s="25">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>DrawLogix - 59% complete</t>
+          <t>DrawLogix - 72% complete</t>
         </is>
       </c>
     </row>
@@ -5777,19 +5777,19 @@
           <t>Clash and clearance detection</t>
         </is>
       </c>
-      <c r="C16" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>cad/clash.ts - hard clashes by AABB intersection with overlap volume, plus CLEARANCE breaches against rules held as data. The second is the one that survives coordination: a valve 40mm from a wall is legal geometry and an unserviceable installation. Openings formed for an element suppress its clash; structural involvement raises severity. 19 tests with families.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>No model federation, no clash workflow.</t>
+          <t>Axis-aligned boxes only, so it over-reports on diagonal runs and never under-reports. No IFC import to feed it from a federated model.</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -5814,19 +5814,19 @@
           <t>Smart components and families</t>
         </is>
       </c>
-      <c r="C17" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>library_entry table exists for reusable content.</t>
+          <t>cad/families.ts - typed parameters with constraints, type vs instance scope, and derived parameters computed rather than stored. Warns when an instance overrides a type parameter, which looks like it worked and does not propagate. Formula evaluation is a deliberately tiny arithmetic language, not a general evaluator, because family definitions are data that can arrive from a library.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>No parametric component definitions with parameters, connectors, constraints or quantity rules.</t>
+          <t>No family editor UI; families are defined in code or supplied as data.</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
@@ -5982,7 +5982,7 @@
     <row r="1" ht="24" customHeight="1" s="25">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>QuantLogix - 59% complete</t>
+          <t>QuantLogix - 82% complete</t>
         </is>
       </c>
     </row>
@@ -6079,19 +6079,19 @@
           <t>Configurable measurement rules</t>
         </is>
       </c>
-      <c r="C6" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Measurement logic is in code, not data.</t>
+          <t>boq/rules.ts + measurement_rule_set / measurement_rule tables (024). Rules as ordered data with kind, threshold, value and a standard reference; measure() returns the working, not just the answer. Rule sets are versioned rather than edited, so a quantity measured last month stays explainable. NRM2 masonry set included. 17 tests.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>No measurement_rule table, no versioned rule expressions, no standard references (NRM, POMI, CESMM).</t>
+          <t>No screen to author rule sets; a project gets the built-in NRM2 set until one is supplied.</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
@@ -6264,19 +6264,19 @@
           <t>BOQ line to source object trace</t>
         </is>
       </c>
-      <c r="C11" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>pcm_boq_map, pcm_quantity, artifact_provenance, trace endpoints; source_region now exists and is deployed.</t>
+          <t>Takeoff now writes source_region per measurement: bim/takeoff.ts carries element_ids (including for counted categories, so one '120 nr' line still anchors all 120), and the takeoff route anchors each artifact with method 'rule'. regionsFor() reads it back.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>The anchor exists but QuantLogix does not write regions yet - takeoff must record the polygon it measured.</t>
+          <t>Anchors are model-object ids; drawing-page polygons still come only from document extraction.</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -6338,19 +6338,19 @@
           <t>Quantity dirty propagation and remeasure</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C13" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>pcm_quantity has a status column; cad/impact.ts identifies affected measurements.</t>
+          <t>boq/dirty.ts - staleness is state a quantity carries, propagated to anything derived from it, so a bill cannot be assembled from stale parts. Deleted sources supersede rather than stale, so the queue can be cleared. Confidence is reported by VALUE, not count.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Dirty-mark, queue, recompute pipeline is not wired end to end. Stale quantities can be displayed as current.</t>
+          <t>The recompute itself is still triggered by re-running takeoff rather than by a background worker.</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -6375,19 +6375,19 @@
           <t>BOQ delta between revisions</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>cad/compare.ts produces the geometry delta.</t>
+          <t>boq/delta.ts - matched on line code so a re-worded description is not a replaced bill. Separates a design change (source revision moved, chargeable) from a remeasure (same drawing, our own correction, nobody to bill) and reports the split. baseline() freezes a copy rather than holding the live array.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>No BOQ-level delta report or baseline preservation.</t>
+          <t>The design-change/remeasure split is inferred from whether the source revision moved; a change with no revision recorded falls to remeasure.</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -6469,7 +6469,7 @@
     <row r="1" ht="24" customHeight="1" s="25">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>CostLogix - 62% complete</t>
+          <t>CostLogix - 88% complete</t>
         </is>
       </c>
     </row>
@@ -6714,19 +6714,19 @@
           <t>Earned value (PV, EV, AC, SPI, CPI)</t>
         </is>
       </c>
-      <c r="C10" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>cost/evm.ts - PV/EV/AC with SPI, CPI, EAC (CPI method), ETC, VAC and TCPI. rollUp() earns value from PHYSICAL progress times budget, never from spend, so CPI cannot come out at 1.00 by construction. worstPerformers() names the packages doing the damage. 15 tests.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Requires schedule and cost integration.</t>
+          <t>The engine is complete; feeding it needs progress and actual cost from the platform rather than supplied inputs.</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
@@ -6788,19 +6788,19 @@
           <t>Variation and change pricing</t>
         </is>
       </c>
-      <c r="C12" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C12" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>cost/variations.ts - notice refused after the contractual window with the time-bar stated, instruction refused without an attributed approver and refused above the threshold until quoted. register() splits agreed from instructed-but-unagreed from at-risk, and calls out work started with no instruction. priceChange() prefers a contract rate over a star rate and says which it used.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>No ChangeLogix module exists.</t>
+          <t>Contract terms are supplied per call; no per-project terms table yet.</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
@@ -6845,7 +6845,7 @@
     <row r="1" ht="24" customHeight="1" s="25">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>ScheduleLogix - 53% complete</t>
+          <t>ScheduleLogix - 77% complete</t>
         </is>
       </c>
     </row>
@@ -7164,19 +7164,19 @@
           <t>Reconciliation and migration confidence score</t>
         </is>
       </c>
-      <c r="C12" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C12" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>programme/reconcile.ts - compares an imported programme against ours and scores what survived, weighted by what silently moves dates: a lost link or a substituted calendar costs far more than a rename. An activity that did not arrive at all makes the import untrustworthy whatever the rest scores.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Appendix B requires a signed-off reconciliation package, not an Import Successful message.</t>
+          <t>Reconciles two programmes already in our shape; the XER/XML parsers that would produce the source are not built.</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
@@ -7275,19 +7275,19 @@
           <t>Resources, roles, histogram, levelling</t>
         </is>
       </c>
-      <c r="C15" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>programme/resources.ts - demand per day per role, peak, unit-days, availability windows, and over-allocations merged into periods rather than repeated per day. Roles with no stated availability are reported as an assumption rather than treated as infinite. smoothness() scores how spiky the curve is. 9 tests.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>P1 tier (SL-P6-025, 033, 034).</t>
+          <t>Levelling is deliberately NOT done: resolving an over-allocation means moving activities and changing dates, and a tool that silently rescheduled to fit its own resource assumptions would be worse than one that reports the conflict.</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -7312,19 +7312,19 @@
           <t>Look-ahead and work readiness</t>
         </is>
       </c>
-      <c r="C16" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>programme/lookahead.ts - readiness computed from CONSTRAINTS, not asserted: design, materials, permit, access, predecessor, labour. An activity whose dates say Monday but whose permit clears Friday is blocked, not ready. Constraints with no expected date are separated as unchased, blocked critical work is highlighted, and open constraints group by owner for the meeting. PPC gives no partial credit. 21 tests with what-if and reconciliation.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Named differentiator; depends on connected procurement and drawing data.</t>
+          <t>Constraints are supplied; no automatic linking to the RFI or procurement records that would clear them.</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -7423,19 +7423,19 @@
           <t>What-if sandbox</t>
         </is>
       </c>
-      <c r="C19" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C19" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>programme/whatif.ts - scenarios applied to a COPY and recomputed through cpm.ts. Crash, overlap (fast-track by turning FS into SS+lag), resequence, extend, remove. A change to an activity with float is reported as WASTED with the reason, since money into a non-critical activity moves the finish date not one day. Options ranked by cost per day recovered, not by days.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Compares scenarios; does not commit one back to the live programme.</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
@@ -7480,7 +7480,7 @@
     <row r="1" ht="24" customHeight="1" s="25">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>ProcureLogix - 67% complete</t>
+          <t>ProcureLogix - 92% complete</t>
         </is>
       </c>
     </row>
@@ -7688,19 +7688,19 @@
           <t>Purchase orders and commitments</t>
         </is>
       </c>
-      <c r="C9" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C9" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>procure/commitments.ts - raise/issue/vary/pay with an approver required for any increase and payment beyond the commitment refused. position() reports budget, committed and paid separately, and anticipates final cost from COMMITMENT plus remaining budget, not from payments. 15 tests.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Orders are modelled and reported; no PO document generation or supplier portal.</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -7725,19 +7725,19 @@
           <t>Delivery tracking and long-lead alerts</t>
         </is>
       </c>
-      <c r="C10" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>deliveryAlerts() in procure/commitments.ts computes the shortfall from lead time against the required-on-site date, rather than trusting a promised delivery date, and orders the alerts worst-first.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>The long-lead alerting is done; recording actual deliveries - goods received, partial deliveries against an order - is not, so a part-delivered order cannot yet be tracked line by line.</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">

--- a/Preckon_Module_Completion.xlsx
+++ b/Preckon_Module_Completion.xlsx
@@ -990,7 +990,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -1371,7 +1370,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="39.95" customHeight="1" s="25">
       <c r="A15" s="9" t="inlineStr">
         <is>
@@ -1409,7 +1407,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="41" t="inlineStr">
         <is>
@@ -1502,7 +1499,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3940,7 +3936,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -4686,7 +4681,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -5260,12 +5254,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>doc/register-panel.tsx, mounted as a Register tab beside Intake on the documents page - register table with late-flagging, registration drawer driven by the scheme's own segments (422 shown per segment, no number burned), per-document drawer with revisions, send-for-review, decide, issue, and a transmittals table.</t>
+          <t>doc/register-panel.tsx, mounted as a Register tab beside Intake on the documents page - register table with late-flagging, registration drawer driven by the scheme's own segments (422 shown per segment, no number burned), and a per-document drawer with revisions, send-for-review, record-decision and issue (which surfaces the 409 review gate). Transmittals are LISTED on the same screen.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>One screen covering register, revisions, review and transmittals; distribution lists and retention still have no UI.</t>
+          <t>Read-only for transmittals: creating and sending one is still API-only, as are distribution lists and retention. So the register, revision, review and issue flow is usable from the UI; the rest of DocLogix is not.</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -5321,7 +5315,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -5993,7 +5986,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -6480,7 +6472,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -6856,7 +6847,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -7491,7 +7481,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -7793,7 +7782,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>

--- a/Preckon_Module_Completion.xlsx
+++ b/Preckon_Module_Completion.xlsx
@@ -7,29 +7,30 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TenderLogix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DocLogix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DrawLogix" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuantLogix" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CostLogix" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScheduleLogix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProcureLogix" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NarrativeLogix" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform-Core" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P0 Backlog" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blueprints" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TenderLogix" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DocLogix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DrawLogix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuantLogix" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CostLogix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScheduleLogix" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProcureLogix" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NarrativeLogix" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform-Core" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P0 Backlog" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'TenderLogix'!$A$4:$G$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DocLogix'!$A$4:$G$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DrawLogix'!$A$4:$G$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QuantLogix'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CostLogix'!$A$4:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'ScheduleLogix'!$A$4:$G$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ProcureLogix'!$A$4:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'NarrativeLogix'!$A$4:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Platform-Core'!$A$4:$G$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'P0 Backlog'!$A$4:$F$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TenderLogix'!$A$4:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DocLogix'!$A$4:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DrawLogix'!$A$4:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'QuantLogix'!$A$4:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CostLogix'!$A$4:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ScheduleLogix'!$A$4:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'ProcureLogix'!$A$4:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NarrativeLogix'!$A$4:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Platform-Core'!$A$4:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'P0 Backlog'!$A$4:$F$20</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,8 +136,24 @@
       <b val="1"/>
       <color rgb="000B1B2B"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B1B2B"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00475569"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -193,8 +210,13 @@
         <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000B1B2B"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -232,11 +254,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E3E8EF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E3E8EF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E3E8EF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E3E8EF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -376,6 +412,29 @@
     <xf numFmtId="0" fontId="14" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -986,10 +1045,11 @@
     <row r="2" ht="18" customHeight="1" s="25">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Every feature verified against the codebase and the deployed database on 20 Aug 2026, after the 16:05 deploy (app and worker rebuilt, 23 migrations applied). Weighted: Done 1.0, Partial 0.5, Scaffolded 0.25, Missing 0. Each module's percentage is computed from its own sheet, and the P0 Backlog is generated from those same rows - so the dashboard, the detail and the backlog cannot disagree. 841 tests pass across 38 files.</t>
-        </is>
-      </c>
-    </row>
+          <t>Every feature verified against the codebase and the deployed database on 21 Aug 2026. Weighted: Done 1.0, Partial 0.5, Scaffolded 0.25, Missing 0. Module percentages are computed from each module's own sheet; the P0 Backlog and the Blueprints page are generated from those same rows, so the four cannot disagree. 982 tests pass across 46 files; 24 migrations and 84 tables are live on the deployed database.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -1348,20 +1408,20 @@
         <v>40</v>
       </c>
       <c r="D13" s="29" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E13" s="30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" s="31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13" s="32" t="n">
-        <v>0.6</v>
+        <v>0.675</v>
       </c>
       <c r="H13" s="33" t="inlineStr">
         <is>
-          <t>████████████░░░░░░░░</t>
+          <t>██████████████░░░░░░</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1370,6 +1430,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="39.95" customHeight="1" s="25">
       <c r="A15" s="9" t="inlineStr">
         <is>
@@ -1385,20 +1446,20 @@
         <v>132</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" s="38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G15" s="39" t="n">
-        <v>0.754</v>
+        <v>0.777</v>
       </c>
       <c r="H15" s="40" t="inlineStr">
         <is>
-          <t>███████████████░░░░░</t>
+          <t>████████████████░░░░</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -1407,6 +1468,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="41" t="inlineStr">
         <is>
@@ -1468,6 +1530,197 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="25" min="1" max="1"/>
+    <col width="44" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="54" customWidth="1" style="25" min="4" max="4"/>
+    <col width="60" customWidth="1" style="25" min="5" max="5"/>
+    <col width="9" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8" customWidth="1" style="25" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>NarrativeLogix - 83% complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="25">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Technical narrative and proposal writing.  3 features audited: 2 done, 1 partial, 0 missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="33.95" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Evidence in code / DB</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Gap - what is still needed</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25.5" customHeight="1" s="25">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Drafting</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Technical narrative sections</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>narrative_section artifact type; agent.narrative; workflow.narrativelogix; surfaces/narrative.tsx.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Export</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Narrative export to markdown</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>narrative/export.md endpoint.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25.5" customHeight="1" s="25">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Narrative grounded in project evidence</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sections reference artifacts.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>No retrieval layer, so grounding is limited to what is passed in the envelope.</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1488,7 +1741,7 @@
     <row r="1" ht="24" customHeight="1" s="25">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>Platform / Core - 60% complete</t>
+          <t>Platform / Core - 68% complete</t>
         </is>
       </c>
     </row>
@@ -1499,6 +1752,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -2287,19 +2541,19 @@
           <t>Metrics, tracing, dashboards</t>
         </is>
       </c>
-      <c r="C25" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C25" s="47" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>trace_id exists on ai_job but no OpenTelemetry.</t>
+          <t>/api/v1/metrics in Prometheus text format: jobs by status, queue depth, age of the oldest queued job, attempts/spend/tokens by execution class, policy refusals, tenants, projects, registered documents. Live and returning real figures.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>No metrics endpoint, no dashboards, no alerting.</t>
+          <t>Metrics only. No distributed tracing (trace_id exists on ai_job and nothing collects it) and no dashboards or alerting - a scraper still has to be pointed at this.</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -2324,19 +2578,19 @@
           <t>AI cost reporting</t>
         </is>
       </c>
-      <c r="C26" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>ai-cost.ts; /api/v1/ai-cost. 19 tests.</t>
+          <t>ai-cost.ts now reads ai_usage_ledger - one row per ATTEMPT - unioned with ai_job for jobs predating the ledger, so retries are counted going forward and no historic month disappears. Stub detection reads execution_class.</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Built on under-counted data until the per-attempt ledger exists.</t>
+          <t>Reports spend; no per-tenant billing export yet.</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -2546,19 +2800,19 @@
           <t>Automated backup and tested restore</t>
         </is>
       </c>
-      <c r="C32" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C32" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>scripts/backup.sh dumps with --single-transaction --routines --triggers (the audit chain lives in a stored procedure), then RESTORES into a scratch database and compares row counts on audit_event, artifact, project, document_register and ai_usage_ledger before keeping the file. Verified on the server: 84 tables, 2,878 audit events restored and matching. Nightly at 02:15 via cron, logged to /var/log/preckon-backup.log, 14 kept.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>An untested restore is not a backup.</t>
+          <t>Backups are local to the host. Off-site copy is the remaining risk - a server that loses its disk loses the backups with it.</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
@@ -2842,19 +3096,19 @@
           <t>Upload validation and scan gating</t>
         </is>
       </c>
-      <c r="C40" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C40" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>upload-safety.ts - magic-number vs extension, blocked extensions, macro formats, path traversal, zip-bomb ratio, explicit scan states. 33 tests.</t>
+          <t>checkUpload() is called in the files upload route before anything is written: extension against magic number, blocked executable types, path separators in the name, size ceiling. Checked on the bytes, because the declared mime type comes from the client.</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Explicitly not an antivirus. A real scanner still needs to sit behind it, and the upload route does not call this yet.</t>
+          <t>Explicitly not an antivirus - it closes the cheap holes and a real scanner still belongs behind it.</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr">
@@ -2879,19 +3133,19 @@
           <t>Port hardening</t>
         </is>
       </c>
-      <c r="C41" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C41" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3308, 4000 and 8081 bind to 127.0.0.1 and are externally closed.</t>
+          <t>firewalld permitted 11434 (Ollama, unauthenticated), 5173 (Vite dev port, nothing listening) and 8081 (bound to 127.0.0.1, so the rule granted nothing). All three removed and reloaded; app verified healthy after. The earlier note that 3306/3307 were exposed was wrong - firewalld never permitted them and neither answers from the internet.</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>3307 (MySQL), 11434 (Ollama, unauthenticated) and 5000 bind 0.0.0.0; only the provider firewall stops them.</t>
+          <t>5000 and 8090 remain permitted and both have something listening. They need a decision about what they are for rather than a guess.</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
@@ -3026,7 +3280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3618,7 +3872,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3738,11 +3992,11 @@
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Was 77 on 20 Aug. ProcureLogix added 5: vendor, rfq, rfq_vendor, quote, quote_line - all declared in schema.sql as well as the migration.</t>
+          <t>Deployed. ProcureLogix added 5 and QuantLogix's measurement rules added 2; all declared in schema.sql as well as their migrations.</t>
         </is>
       </c>
     </row>
@@ -3753,11 +4007,11 @@
         </is>
       </c>
       <c r="B10" s="18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>021 AI governance, 022 model registry seed, 023 procurement. All re-runnable and applied to production.</t>
+          <t>019-020 DocLogix, 021 AI governance, 022 model registry seed, 023 procurement, 024 measurement rules. All re-runnable and applied to production.</t>
         </is>
       </c>
     </row>
@@ -3767,14 +4021,12 @@
           <t>API routes</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="B11" s="18" t="n">
+        <v>90</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Was 78. Seven new DocLogix endpoints plus search</t>
+          <t>Adds document reviews, review decisions and /api/v1/metrics.</t>
         </is>
       </c>
     </row>
@@ -3803,12 +4055,12 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>841 passing</t>
+          <t>982 passing</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>38 files. Was 753. Procurement added 23, cost 21, programme 21, tender scope and clarifications 12.</t>
+          <t>46 files. Was 426 on 19 Aug. The two failures in a local run are a MySQL the dev machine does not have; they pass where a database exists.</t>
         </is>
       </c>
     </row>
@@ -3819,11 +4071,11 @@
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>cpm, pcm/measure, boq/reconcile, cad/compare, cad/impact, standards, doc/numbering, doc/revision, doc/compare, doc/review, doc/retention, ai/govern, plus the 13 added on 20 Aug: procure rfq/quotes/coverage, cost waterfall/rates/scenarios/cashflow, programme calendars/baselines/progress/health, tender scope/clarifications.</t>
+          <t>cpm, pcm/measure, boq reconcile/rules/delta/dirty, cad compare/impact/clash/families, doc numbering/revision/compare/review/retention, ai govern, procure rfq/quotes/coverage/commitments, cost waterfall/rates/scenarios/cashflow/evm/variations, programme calendars/baselines/progress/health/lookahead/whatif/reconcile/resources, tender scope/clarifications/requirements/addenda/positions/readiness/outcome.</t>
         </is>
       </c>
     </row>
@@ -3867,14 +4119,12 @@
           <t>CI runs</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="B17" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Six workflow files exist; none has ever executed. 632 tests run only on a developer machine.</t>
+          <t>Six workflow files exist; none has ever executed. The publishing token lacks `workflow` scope, so ci.yml cannot even reach the tenant mirror. Granting that scope is the cheapest open P0.</t>
         </is>
       </c>
     </row>
@@ -3905,6 +4155,364 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" style="25" min="1" max="1"/>
+    <col width="8" customWidth="1" style="25" min="2" max="2"/>
+    <col width="52" customWidth="1" style="25" min="3" max="3"/>
+    <col width="22" customWidth="1" style="25" min="4" max="4"/>
+    <col width="10" customWidth="1" style="25" min="5" max="5"/>
+    <col width="88" customWidth="1" style="25" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>The blueprints against what exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1" s="25">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Every specification document in Documents/, what it asks for, and where that landed. Percentages are read from the module sheets in this workbook, so this page cannot drift from the dashboard. Line counts are the documents' own size - a reminder that a 2,876-line blueprint and a 165-line one are not the same promise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="52" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="B4" s="52" t="inlineStr">
+        <is>
+          <t>Lines</t>
+        </is>
+      </c>
+      <c r="C4" s="52" t="inlineStr">
+        <is>
+          <t>What it specifies</t>
+        </is>
+      </c>
+      <c r="D4" s="52" t="inlineStr">
+        <is>
+          <t>Implemented in</t>
+        </is>
+      </c>
+      <c r="E4" s="52" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="F4" s="52" t="inlineStr">
+        <is>
+          <t>Where it actually stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="53" t="inlineStr">
+        <is>
+          <t>Preckon_Master_Blueprint_v1.0</t>
+        </is>
+      </c>
+      <c r="B5" s="54" t="n">
+        <v>2402</v>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>The platform as a whole: two planes, the module set, the artifact chain, lifecycle and entitlements.</t>
+        </is>
+      </c>
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>Platform / Core</t>
+        </is>
+      </c>
+      <c r="E5" s="57" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>The chain is real: typed artifacts, provenance, review gates, a tamper-evident audit chain and durable jobs. The two-plane split exists (host + tenant). What the document budgets and the build does not have is the enterprise operations layer around it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>Preckon_Complete_Platform_Blueprint_v1.1</t>
+        </is>
+      </c>
+      <c r="B6" s="54" t="n">
+        <v>486</v>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>Platform section 15 onward: identity, security, integration hub, knowledge graph.</t>
+        </is>
+      </c>
+      <c r="D6" s="56" t="inlineStr">
+        <is>
+          <t>Platform / Core</t>
+        </is>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="F6" s="55" t="inlineStr">
+        <is>
+          <t>Identity, RBAC, tenancy and audit are built. SSO, MFA, SCIM, encryption at rest and the connector SDK are not - the first three are code nobody has written yet, the last two need infrastructure decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="53" t="inlineStr">
+        <is>
+          <t>Preckon_AI_Fabric_Master_Blueprint_Implementation_v1.1</t>
+        </is>
+      </c>
+      <c r="B7" s="54" t="n">
+        <v>2876</v>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>AI governance: deployment modes, data sensitivity, model and prompt registries, budgets, caching, retrieval, usage metering.</t>
+        </is>
+      </c>
+      <c r="D7" s="56" t="inlineStr">
+        <is>
+          <t>Platform / Core</t>
+        </is>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="F7" s="55" t="inlineStr">
+        <is>
+          <t>Landed on 20 Aug and now WIRED, not just written: policy, model registry and budgets are consulted on every enqueue and every attempt is metered to ai_usage_ledger. Enforcement is deliberately report-only - unclassified data defaults to confidential, which saas mode forbids sending externally, so switching it on today would stop every job. Prompt registry and response cache have tables and logic and no caller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>Preckon_PCM_Engineering_Blueprint_v1.1</t>
+        </is>
+      </c>
+      <c r="B8" s="54" t="n">
+        <v>2279</v>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>The Project Coordinate Model: objects, units, relationships, provenance regions, traceability.</t>
+        </is>
+      </c>
+      <c r="D8" s="56" t="inlineStr">
+        <is>
+          <t>QuantLogix, DrawLogix</t>
+        </is>
+      </c>
+      <c r="E8" s="57" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="F8" s="55" t="inlineStr">
+        <is>
+          <t>pcm objects, units, relationships and source_region all exist, and takeoff now writes a region per measurement so a quantity anchors to the elements it came from. The knowledge-graph traversal the document describes is PCM-scoped only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>DocLogix_Engineering_PRD_PCM_v1.0</t>
+        </is>
+      </c>
+      <c r="B9" s="54" t="n">
+        <v>2602</v>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>CDE, document control, numbering, revisions, transmittals, review, distribution, retention, retrieval.</t>
+        </is>
+      </c>
+      <c r="D9" s="56" t="inlineStr">
+        <is>
+          <t>DocLogix</t>
+        </is>
+      </c>
+      <c r="E9" s="58" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="F9" s="55" t="inlineStr">
+        <is>
+          <t>The most complete module in the build: 14 of 15 features, with the register, revisions, review gate, issue and transmittals now usable from a screen rather than only over HTTP. OCR is the single gap and needs an engine, not a file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="53" t="inlineStr">
+        <is>
+          <t>Preckon_TenderLogix_Blueprint_v2.0</t>
+        </is>
+      </c>
+      <c r="B10" s="54" t="n">
+        <v>165</v>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>Tender engineering and bid orchestration: requirements, compliance, addenda, risk, submission, award.</t>
+        </is>
+      </c>
+      <c r="D10" s="56" t="inlineStr">
+        <is>
+          <t>TenderLogix</t>
+        </is>
+      </c>
+      <c r="E10" s="58" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="F10" s="55" t="inlineStr">
+        <is>
+          <t>Requirements-with-citation, the compliance matrix, addendum impact, risk and commercial positions, weighted readiness, the manifest and win/loss analysis are built. Negotiation/BAFO, bid strategy and handover are not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>Preckon_DrawLogix_Complete_Blueprint_v1.0</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="n">
+        <v>427</v>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>Drawing, design, BIM, documentation and drawing intelligence.</t>
+        </is>
+      </c>
+      <c r="D11" s="56" t="inlineStr">
+        <is>
+          <t>DrawLogix</t>
+        </is>
+      </c>
+      <c r="E11" s="57" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F11" s="55" t="inlineStr">
+        <is>
+          <t>Intake, viewer, takeoff, revision compare, the AI copilot, clash and clearance detection and parametric families exist. IFC, symbol recognition, 3D authoring and federated-model clash are engine projects rather than domain logic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="53" t="inlineStr">
+        <is>
+          <t>Preckon_DrawLogix_Studio_Web_Architecture_and_Design_v1.0</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>The browser CAD/BIM studio: command set, sheets, tags, dimensions, desktop client.</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="inlineStr">
+        <is>
+          <t>DrawLogix</t>
+        </is>
+      </c>
+      <c r="E12" s="57" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F12" s="55" t="inlineStr">
+        <is>
+          <t>The studio exists in the browser and in the desktop workstation, which converts DWG locally. The deterministic command set and sheets/tags/dimensions are partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="53" t="inlineStr">
+        <is>
+          <t>Preckon_ScheduleLogix_Blueprint_v1.1</t>
+        </is>
+      </c>
+      <c r="B13" s="54" t="n">
+        <v>485</v>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>Primavera-class scheduling: migration from P6, calendars, baselines, progress, resources, delay intelligence.</t>
+        </is>
+      </c>
+      <c r="D13" s="56" t="inlineStr">
+        <is>
+          <t>ScheduleLogix</t>
+        </is>
+      </c>
+      <c r="E13" s="57" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="F13" s="55" t="inlineStr">
+        <is>
+          <t>CPM, calendars (Gulf and western weeks), baselines that refuse an unexplained re-baseline, progress at a data date, DCMA-style health scoring, look-ahead readiness, what-if recovery and reconciliation confidence are built. The migration-first mission is not: P6 XER and XML import remain unwritten, and without them reconciliation has no source to read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="53" t="inlineStr">
+        <is>
+          <t>Preckon_Construction_Knowledge_Graph_Blueprint_v1.0</t>
+        </is>
+      </c>
+      <c r="B14" s="54" t="n">
+        <v>102</v>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>A typed graph across modules: entities, relationships, traversal.</t>
+        </is>
+      </c>
+      <c r="D14" s="56" t="inlineStr">
+        <is>
+          <t>Platform / Core</t>
+        </is>
+      </c>
+      <c r="E14" s="57" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="F14" s="55" t="inlineStr">
+        <is>
+          <t>pcm_relationship holds typed edges with source and confidence, but only within PCM. The Doc-Draw-Quant-Cost-Schedule traversal the document describes does not exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="59" t="inlineStr">
+        <is>
+          <t>Documents that describe work not yet started are still counted in the module sheets as Missing rows — nothing here is excluded for being inconvenient.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3936,6 +4544,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -4649,7 +5258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4681,6 +5290,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -5283,7 +5893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5315,6 +5925,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -5954,7 +6565,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5986,6 +6597,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -6440,7 +7052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6472,6 +7084,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -6815,7 +7428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6847,6 +7460,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -7449,7 +8063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7481,6 +8095,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="33.95" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -7748,194 +8363,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" style="25" min="1" max="1"/>
-    <col width="44" customWidth="1" style="25" min="2" max="2"/>
-    <col width="12" customWidth="1" style="25" min="3" max="3"/>
-    <col width="54" customWidth="1" style="25" min="4" max="4"/>
-    <col width="60" customWidth="1" style="25" min="5" max="5"/>
-    <col width="9" customWidth="1" style="25" min="6" max="6"/>
-    <col width="8" customWidth="1" style="25" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="25">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>NarrativeLogix - 83% complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" s="25">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>Technical narrative and proposal writing.  3 features audited: 2 done, 1 partial, 0 missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="33.95" customHeight="1" s="25">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Evidence in code / DB</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>Gap - what is still needed</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>Effort</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25.5" customHeight="1" s="25">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Drafting</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Technical narrative sections</t>
-        </is>
-      </c>
-      <c r="C5" s="46" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>narrative_section artifact type; agent.narrative; workflow.narrativelogix; surfaces/narrative.tsx.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Export</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Narrative export to markdown</t>
-        </is>
-      </c>
-      <c r="C6" s="46" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>narrative/export.md endpoint.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25.5" customHeight="1" s="25">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Narrative grounded in project evidence</t>
-        </is>
-      </c>
-      <c r="C7" s="47" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Sections reference artifacts.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>No retrieval layer, so grounding is limited to what is passed in the envelope.</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:G7"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Preckon_Module_Completion.xlsx
+++ b/Preckon_Module_Completion.xlsx
@@ -1408,16 +1408,16 @@
         <v>40</v>
       </c>
       <c r="D13" s="29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G13" s="32" t="n">
-        <v>0.675</v>
+        <v>0.725</v>
       </c>
       <c r="H13" s="33" t="inlineStr">
         <is>
@@ -1446,16 +1446,16 @@
         <v>132</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E15" s="37" t="n">
         <v>15</v>
       </c>
       <c r="F15" s="38" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G15" s="39" t="n">
-        <v>0.777</v>
+        <v>0.792</v>
       </c>
       <c r="H15" s="40" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
     <row r="1" ht="24" customHeight="1" s="25">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>Platform / Core - 68% complete</t>
+          <t>Platform / Core - 72% complete</t>
         </is>
       </c>
     </row>
@@ -1875,19 +1875,19 @@
           <t>MFA</t>
         </is>
       </c>
-      <c r="C7" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C7" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Only i18n strings exist; no implementation.</t>
+          <t>Better Auth's two-factor plugin: TOTP with ten single-use backup codes, twoFactor table and user.twoFactorEnabled live (migration 025). Endpoints answer under /api/auth/two-factor/*. skipVerificationOnEnable is off, so a user proves a code works before the factor is switched on - enabling first locks out anyone whose authenticator was set up wrong, and a broken second factor cannot be used to recover from itself.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Enterprise deal blocker.</t>
+          <t>No enrolment screen yet; the endpoints work and the UI to walk a user through a QR code is not built. No enforcement policy that REQUIRES MFA for a role.</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -1912,19 +1912,19 @@
           <t>SCIM provisioning</t>
         </is>
       </c>
-      <c r="C8" s="48" t="inlineStr">
-        <is>
-          <t>Missing</t>
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>SCIM 2.0 at /scim/v2/Users - the RFC path, since providers construct it themselves. List with userName/externalId filter, create, replace, patch and delete. DELETE suspends rather than deletes so approvals and audit entries stay attributable. The patch handler accepts Azure's Replace-with-path, Okta's pathless value object, filtered paths and the string True, and reports anything it cannot parse as a 400 rather than a silent 200 the IdP would record as a successful deprovision. Per-tenant bearer tokens (migration 026). 17 tests.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Users only - no Groups resource, so role assignment is still done in the app rather than driven from the directory.</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
